--- a/data/reference/Unidades/plantilla_modelos_ZVEH_ZCAM.xlsx
+++ b/data/reference/Unidades/plantilla_modelos_ZVEH_ZCAM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sherrera\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tattersall-my.sharepoint.com/personal/sherrera_tattersall_cl/Documents/Escritorio/FACU/INPUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF803BB-BA08-4F01-AE46-9292D853ED64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -3086,7 +3086,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3122,41 +3122,39 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -3187,39 +3185,6 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3581,8 +3546,8 @@
   <cols>
     <col min="1" max="1" width="19.85546875" style="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="18.5703125" style="19" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" style="19" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" style="19" customWidth="1"/>
@@ -3713,11 +3678,11 @@
         <v>1</v>
       </c>
       <c r="R2" s="21">
-        <f>IF(C2="","",LEN(C2))</f>
+        <f t="shared" ref="R2:R33" si="0">IF(C2="","",LEN(C2))</f>
         <v>35</v>
       </c>
       <c r="S2" s="21">
-        <f>IF(D2="","",LEN(D2))</f>
+        <f t="shared" ref="S2:S33" si="1">IF(D2="","",LEN(D2))</f>
         <v>30</v>
       </c>
     </row>
@@ -3731,11 +3696,11 @@
         <v/>
       </c>
       <c r="R3" s="21" t="str">
-        <f>IF(C3="","",LEN(C3))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S3" s="21" t="str">
-        <f>IF(D3="","",LEN(D3))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3750,11 +3715,11 @@
       </c>
       <c r="E4" s="22"/>
       <c r="R4" s="21" t="str">
-        <f>IF(C4="","",LEN(C4))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S4" s="21" t="str">
-        <f>IF(D4="","",LEN(D4))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3768,11 +3733,11 @@
         <v/>
       </c>
       <c r="R5" s="21" t="str">
-        <f>IF(C5="","",LEN(C5))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S5" s="21" t="str">
-        <f>IF(D5="","",LEN(D5))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3786,11 +3751,11 @@
         <v/>
       </c>
       <c r="R6" s="21" t="str">
-        <f>IF(C6="","",LEN(C6))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S6" s="21" t="str">
-        <f>IF(D6="","",LEN(D6))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3804,11 +3769,11 @@
         <v/>
       </c>
       <c r="R7" s="21" t="str">
-        <f>IF(C7="","",LEN(C7))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S7" s="21" t="str">
-        <f>IF(D7="","",LEN(D7))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3822,11 +3787,11 @@
         <v/>
       </c>
       <c r="R8" s="21" t="str">
-        <f>IF(C8="","",LEN(C8))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S8" s="21" t="str">
-        <f>IF(D8="","",LEN(D8))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3840,11 +3805,11 @@
         <v/>
       </c>
       <c r="R9" s="21" t="str">
-        <f>IF(C9="","",LEN(C9))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S9" s="21" t="str">
-        <f>IF(D9="","",LEN(D9))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3858,11 +3823,11 @@
         <v/>
       </c>
       <c r="R10" s="21" t="str">
-        <f>IF(C10="","",LEN(C10))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S10" s="21" t="str">
-        <f>IF(D10="","",LEN(D10))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3876,11 +3841,11 @@
         <v/>
       </c>
       <c r="R11" s="21" t="str">
-        <f>IF(C11="","",LEN(C11))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S11" s="21" t="str">
-        <f>IF(D11="","",LEN(D11))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3894,11 +3859,11 @@
         <v/>
       </c>
       <c r="R12" s="21" t="str">
-        <f>IF(C12="","",LEN(C12))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S12" s="21" t="str">
-        <f>IF(D12="","",LEN(D12))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3912,11 +3877,11 @@
         <v/>
       </c>
       <c r="R13" s="21" t="str">
-        <f>IF(C13="","",LEN(C13))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S13" s="21" t="str">
-        <f>IF(D13="","",LEN(D13))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3930,11 +3895,11 @@
         <v/>
       </c>
       <c r="R14" s="21" t="str">
-        <f>IF(C14="","",LEN(C14))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S14" s="21" t="str">
-        <f>IF(D14="","",LEN(D14))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3948,11 +3913,11 @@
         <v/>
       </c>
       <c r="R15" s="21" t="str">
-        <f>IF(C15="","",LEN(C15))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S15" s="21" t="str">
-        <f>IF(D15="","",LEN(D15))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3966,11 +3931,11 @@
         <v/>
       </c>
       <c r="R16" s="21" t="str">
-        <f>IF(C16="","",LEN(C16))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S16" s="21" t="str">
-        <f>IF(D16="","",LEN(D16))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3984,11 +3949,11 @@
         <v/>
       </c>
       <c r="R17" s="21" t="str">
-        <f>IF(C17="","",LEN(C17))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S17" s="21" t="str">
-        <f>IF(D17="","",LEN(D17))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4002,11 +3967,11 @@
         <v/>
       </c>
       <c r="R18" s="21" t="str">
-        <f>IF(C18="","",LEN(C18))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S18" s="21" t="str">
-        <f>IF(D18="","",LEN(D18))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4020,11 +3985,11 @@
         <v/>
       </c>
       <c r="R19" s="21" t="str">
-        <f>IF(C19="","",LEN(C19))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S19" s="21" t="str">
-        <f>IF(D19="","",LEN(D19))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4038,11 +4003,11 @@
         <v/>
       </c>
       <c r="R20" s="21" t="str">
-        <f>IF(C20="","",LEN(C20))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S20" s="21" t="str">
-        <f>IF(D20="","",LEN(D20))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4056,11 +4021,11 @@
         <v/>
       </c>
       <c r="R21" s="21" t="str">
-        <f>IF(C21="","",LEN(C21))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S21" s="21" t="str">
-        <f>IF(D21="","",LEN(D21))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4074,11 +4039,11 @@
         <v/>
       </c>
       <c r="R22" s="21" t="str">
-        <f>IF(C22="","",LEN(C22))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S22" s="21" t="str">
-        <f>IF(D22="","",LEN(D22))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4092,11 +4057,11 @@
         <v/>
       </c>
       <c r="R23" s="21" t="str">
-        <f>IF(C23="","",LEN(C23))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S23" s="21" t="str">
-        <f>IF(D23="","",LEN(D23))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4110,11 +4075,11 @@
         <v/>
       </c>
       <c r="R24" s="21" t="str">
-        <f>IF(C24="","",LEN(C24))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S24" s="21" t="str">
-        <f>IF(D24="","",LEN(D24))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4128,11 +4093,11 @@
         <v/>
       </c>
       <c r="R25" s="21" t="str">
-        <f>IF(C25="","",LEN(C25))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S25" s="21" t="str">
-        <f>IF(D25="","",LEN(D25))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4146,11 +4111,11 @@
         <v/>
       </c>
       <c r="R26" s="21" t="str">
-        <f>IF(C26="","",LEN(C26))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S26" s="21" t="str">
-        <f>IF(D26="","",LEN(D26))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4164,11 +4129,11 @@
         <v/>
       </c>
       <c r="R27" s="21" t="str">
-        <f>IF(C27="","",LEN(C27))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S27" s="21" t="str">
-        <f>IF(D27="","",LEN(D27))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4182,11 +4147,11 @@
         <v/>
       </c>
       <c r="R28" s="21" t="str">
-        <f>IF(C28="","",LEN(C28))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S28" s="21" t="str">
-        <f>IF(D28="","",LEN(D28))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4200,11 +4165,11 @@
         <v/>
       </c>
       <c r="R29" s="21" t="str">
-        <f>IF(C29="","",LEN(C29))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S29" s="21" t="str">
-        <f>IF(D29="","",LEN(D29))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4218,11 +4183,11 @@
         <v/>
       </c>
       <c r="R30" s="21" t="str">
-        <f>IF(C30="","",LEN(C30))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S30" s="21" t="str">
-        <f>IF(D30="","",LEN(D30))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4236,11 +4201,11 @@
         <v/>
       </c>
       <c r="R31" s="21" t="str">
-        <f>IF(C31="","",LEN(C31))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S31" s="21" t="str">
-        <f>IF(D31="","",LEN(D31))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4254,11 +4219,11 @@
         <v/>
       </c>
       <c r="R32" s="21" t="str">
-        <f>IF(C32="","",LEN(C32))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S32" s="21" t="str">
-        <f>IF(D32="","",LEN(D32))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4272,11 +4237,11 @@
         <v/>
       </c>
       <c r="R33" s="21" t="str">
-        <f>IF(C33="","",LEN(C33))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S33" s="21" t="str">
-        <f>IF(D33="","",LEN(D33))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4290,11 +4255,11 @@
         <v/>
       </c>
       <c r="R34" s="21" t="str">
-        <f>IF(C34="","",LEN(C34))</f>
+        <f t="shared" ref="R34:R65" si="2">IF(C34="","",LEN(C34))</f>
         <v/>
       </c>
       <c r="S34" s="21" t="str">
-        <f>IF(D34="","",LEN(D34))</f>
+        <f t="shared" ref="S34:S65" si="3">IF(D34="","",LEN(D34))</f>
         <v/>
       </c>
     </row>
@@ -4308,11 +4273,11 @@
         <v/>
       </c>
       <c r="R35" s="21" t="str">
-        <f>IF(C35="","",LEN(C35))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S35" s="21" t="str">
-        <f>IF(D35="","",LEN(D35))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4326,11 +4291,11 @@
         <v/>
       </c>
       <c r="R36" s="21" t="str">
-        <f>IF(C36="","",LEN(C36))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S36" s="21" t="str">
-        <f>IF(D36="","",LEN(D36))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4344,11 +4309,11 @@
         <v/>
       </c>
       <c r="R37" s="21" t="str">
-        <f>IF(C37="","",LEN(C37))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S37" s="21" t="str">
-        <f>IF(D37="","",LEN(D37))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4362,11 +4327,11 @@
         <v/>
       </c>
       <c r="R38" s="21" t="str">
-        <f>IF(C38="","",LEN(C38))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S38" s="21" t="str">
-        <f>IF(D38="","",LEN(D38))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4380,11 +4345,11 @@
         <v/>
       </c>
       <c r="R39" s="21" t="str">
-        <f>IF(C39="","",LEN(C39))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S39" s="21" t="str">
-        <f>IF(D39="","",LEN(D39))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4398,11 +4363,11 @@
         <v/>
       </c>
       <c r="R40" s="21" t="str">
-        <f>IF(C40="","",LEN(C40))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S40" s="21" t="str">
-        <f>IF(D40="","",LEN(D40))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4416,11 +4381,11 @@
         <v/>
       </c>
       <c r="R41" s="21" t="str">
-        <f>IF(C41="","",LEN(C41))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S41" s="21" t="str">
-        <f>IF(D41="","",LEN(D41))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4434,11 +4399,11 @@
         <v/>
       </c>
       <c r="R42" s="21" t="str">
-        <f>IF(C42="","",LEN(C42))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S42" s="21" t="str">
-        <f>IF(D42="","",LEN(D42))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4452,11 +4417,11 @@
         <v/>
       </c>
       <c r="R43" s="21" t="str">
-        <f>IF(C43="","",LEN(C43))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S43" s="21" t="str">
-        <f>IF(D43="","",LEN(D43))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4470,11 +4435,11 @@
         <v/>
       </c>
       <c r="R44" s="21" t="str">
-        <f>IF(C44="","",LEN(C44))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S44" s="21" t="str">
-        <f>IF(D44="","",LEN(D44))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4488,11 +4453,11 @@
         <v/>
       </c>
       <c r="R45" s="21" t="str">
-        <f>IF(C45="","",LEN(C45))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S45" s="21" t="str">
-        <f>IF(D45="","",LEN(D45))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4506,11 +4471,11 @@
         <v/>
       </c>
       <c r="R46" s="21" t="str">
-        <f>IF(C46="","",LEN(C46))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S46" s="21" t="str">
-        <f>IF(D46="","",LEN(D46))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4524,11 +4489,11 @@
         <v/>
       </c>
       <c r="R47" s="21" t="str">
-        <f>IF(C47="","",LEN(C47))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S47" s="21" t="str">
-        <f>IF(D47="","",LEN(D47))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4542,11 +4507,11 @@
         <v/>
       </c>
       <c r="R48" s="21" t="str">
-        <f>IF(C48="","",LEN(C48))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S48" s="21" t="str">
-        <f>IF(D48="","",LEN(D48))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4560,11 +4525,11 @@
         <v/>
       </c>
       <c r="R49" s="21" t="str">
-        <f>IF(C49="","",LEN(C49))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S49" s="21" t="str">
-        <f>IF(D49="","",LEN(D49))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4578,11 +4543,11 @@
         <v/>
       </c>
       <c r="R50" s="21" t="str">
-        <f>IF(C50="","",LEN(C50))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S50" s="21" t="str">
-        <f>IF(D50="","",LEN(D50))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4596,11 +4561,11 @@
         <v/>
       </c>
       <c r="R51" s="21" t="str">
-        <f>IF(C51="","",LEN(C51))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S51" s="21" t="str">
-        <f>IF(D51="","",LEN(D51))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4614,11 +4579,11 @@
         <v/>
       </c>
       <c r="R52" s="21" t="str">
-        <f>IF(C52="","",LEN(C52))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S52" s="21" t="str">
-        <f>IF(D52="","",LEN(D52))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4632,11 +4597,11 @@
         <v/>
       </c>
       <c r="R53" s="21" t="str">
-        <f>IF(C53="","",LEN(C53))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S53" s="21" t="str">
-        <f>IF(D53="","",LEN(D53))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4650,11 +4615,11 @@
         <v/>
       </c>
       <c r="R54" s="21" t="str">
-        <f>IF(C54="","",LEN(C54))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S54" s="21" t="str">
-        <f>IF(D54="","",LEN(D54))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4668,11 +4633,11 @@
         <v/>
       </c>
       <c r="R55" s="21" t="str">
-        <f>IF(C55="","",LEN(C55))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S55" s="21" t="str">
-        <f>IF(D55="","",LEN(D55))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4686,11 +4651,11 @@
         <v/>
       </c>
       <c r="R56" s="21" t="str">
-        <f>IF(C56="","",LEN(C56))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S56" s="21" t="str">
-        <f>IF(D56="","",LEN(D56))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4704,11 +4669,11 @@
         <v/>
       </c>
       <c r="R57" s="21" t="str">
-        <f>IF(C57="","",LEN(C57))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S57" s="21" t="str">
-        <f>IF(D57="","",LEN(D57))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4722,11 +4687,11 @@
         <v/>
       </c>
       <c r="R58" s="21" t="str">
-        <f>IF(C58="","",LEN(C58))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S58" s="21" t="str">
-        <f>IF(D58="","",LEN(D58))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4740,11 +4705,11 @@
         <v/>
       </c>
       <c r="R59" s="21" t="str">
-        <f>IF(C59="","",LEN(C59))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S59" s="21" t="str">
-        <f>IF(D59="","",LEN(D59))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4758,11 +4723,11 @@
         <v/>
       </c>
       <c r="R60" s="21" t="str">
-        <f>IF(C60="","",LEN(C60))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S60" s="21" t="str">
-        <f>IF(D60="","",LEN(D60))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4776,11 +4741,11 @@
         <v/>
       </c>
       <c r="R61" s="21" t="str">
-        <f>IF(C61="","",LEN(C61))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S61" s="21" t="str">
-        <f>IF(D61="","",LEN(D61))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4794,11 +4759,11 @@
         <v/>
       </c>
       <c r="R62" s="21" t="str">
-        <f>IF(C62="","",LEN(C62))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S62" s="21" t="str">
-        <f>IF(D62="","",LEN(D62))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4812,11 +4777,11 @@
         <v/>
       </c>
       <c r="R63" s="21" t="str">
-        <f>IF(C63="","",LEN(C63))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S63" s="21" t="str">
-        <f>IF(D63="","",LEN(D63))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4830,11 +4795,11 @@
         <v/>
       </c>
       <c r="R64" s="21" t="str">
-        <f>IF(C64="","",LEN(C64))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S64" s="21" t="str">
-        <f>IF(D64="","",LEN(D64))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4848,11 +4813,11 @@
         <v/>
       </c>
       <c r="R65" s="21" t="str">
-        <f>IF(C65="","",LEN(C65))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S65" s="21" t="str">
-        <f>IF(D65="","",LEN(D65))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4866,11 +4831,11 @@
         <v/>
       </c>
       <c r="R66" s="21" t="str">
-        <f>IF(C66="","",LEN(C66))</f>
+        <f t="shared" ref="R66:R97" si="4">IF(C66="","",LEN(C66))</f>
         <v/>
       </c>
       <c r="S66" s="21" t="str">
-        <f>IF(D66="","",LEN(D66))</f>
+        <f t="shared" ref="S66:S97" si="5">IF(D66="","",LEN(D66))</f>
         <v/>
       </c>
     </row>
@@ -4884,11 +4849,11 @@
         <v/>
       </c>
       <c r="R67" s="21" t="str">
-        <f>IF(C67="","",LEN(C67))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S67" s="21" t="str">
-        <f>IF(D67="","",LEN(D67))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4902,11 +4867,11 @@
         <v/>
       </c>
       <c r="R68" s="21" t="str">
-        <f>IF(C68="","",LEN(C68))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S68" s="21" t="str">
-        <f>IF(D68="","",LEN(D68))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4920,11 +4885,11 @@
         <v/>
       </c>
       <c r="R69" s="21" t="str">
-        <f>IF(C69="","",LEN(C69))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S69" s="21" t="str">
-        <f>IF(D69="","",LEN(D69))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4938,11 +4903,11 @@
         <v/>
       </c>
       <c r="R70" s="21" t="str">
-        <f>IF(C70="","",LEN(C70))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S70" s="21" t="str">
-        <f>IF(D70="","",LEN(D70))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4956,11 +4921,11 @@
         <v/>
       </c>
       <c r="R71" s="21" t="str">
-        <f>IF(C71="","",LEN(C71))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S71" s="21" t="str">
-        <f>IF(D71="","",LEN(D71))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4974,11 +4939,11 @@
         <v/>
       </c>
       <c r="R72" s="21" t="str">
-        <f>IF(C72="","",LEN(C72))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S72" s="21" t="str">
-        <f>IF(D72="","",LEN(D72))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4992,11 +4957,11 @@
         <v/>
       </c>
       <c r="R73" s="21" t="str">
-        <f>IF(C73="","",LEN(C73))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S73" s="21" t="str">
-        <f>IF(D73="","",LEN(D73))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5010,11 +4975,11 @@
         <v/>
       </c>
       <c r="R74" s="21" t="str">
-        <f>IF(C74="","",LEN(C74))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S74" s="21" t="str">
-        <f>IF(D74="","",LEN(D74))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5028,11 +4993,11 @@
         <v/>
       </c>
       <c r="R75" s="21" t="str">
-        <f>IF(C75="","",LEN(C75))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S75" s="21" t="str">
-        <f>IF(D75="","",LEN(D75))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5046,11 +5011,11 @@
         <v/>
       </c>
       <c r="R76" s="21" t="str">
-        <f>IF(C76="","",LEN(C76))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S76" s="21" t="str">
-        <f>IF(D76="","",LEN(D76))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5064,11 +5029,11 @@
         <v/>
       </c>
       <c r="R77" s="21" t="str">
-        <f>IF(C77="","",LEN(C77))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S77" s="21" t="str">
-        <f>IF(D77="","",LEN(D77))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5082,11 +5047,11 @@
         <v/>
       </c>
       <c r="R78" s="21" t="str">
-        <f>IF(C78="","",LEN(C78))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S78" s="21" t="str">
-        <f>IF(D78="","",LEN(D78))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5100,11 +5065,11 @@
         <v/>
       </c>
       <c r="R79" s="21" t="str">
-        <f>IF(C79="","",LEN(C79))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S79" s="21" t="str">
-        <f>IF(D79="","",LEN(D79))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5118,11 +5083,11 @@
         <v/>
       </c>
       <c r="R80" s="21" t="str">
-        <f>IF(C80="","",LEN(C80))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S80" s="21" t="str">
-        <f>IF(D80="","",LEN(D80))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5136,11 +5101,11 @@
         <v/>
       </c>
       <c r="R81" s="21" t="str">
-        <f>IF(C81="","",LEN(C81))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S81" s="21" t="str">
-        <f>IF(D81="","",LEN(D81))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5154,11 +5119,11 @@
         <v/>
       </c>
       <c r="R82" s="21" t="str">
-        <f>IF(C82="","",LEN(C82))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S82" s="21" t="str">
-        <f>IF(D82="","",LEN(D82))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5172,11 +5137,11 @@
         <v/>
       </c>
       <c r="R83" s="21" t="str">
-        <f>IF(C83="","",LEN(C83))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S83" s="21" t="str">
-        <f>IF(D83="","",LEN(D83))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5190,11 +5155,11 @@
         <v/>
       </c>
       <c r="R84" s="21" t="str">
-        <f>IF(C84="","",LEN(C84))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S84" s="21" t="str">
-        <f>IF(D84="","",LEN(D84))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5208,11 +5173,11 @@
         <v/>
       </c>
       <c r="R85" s="21" t="str">
-        <f>IF(C85="","",LEN(C85))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S85" s="21" t="str">
-        <f>IF(D85="","",LEN(D85))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5226,11 +5191,11 @@
         <v/>
       </c>
       <c r="R86" s="21" t="str">
-        <f>IF(C86="","",LEN(C86))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S86" s="21" t="str">
-        <f>IF(D86="","",LEN(D86))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5244,11 +5209,11 @@
         <v/>
       </c>
       <c r="R87" s="21" t="str">
-        <f>IF(C87="","",LEN(C87))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S87" s="21" t="str">
-        <f>IF(D87="","",LEN(D87))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5262,11 +5227,11 @@
         <v/>
       </c>
       <c r="R88" s="21" t="str">
-        <f>IF(C88="","",LEN(C88))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S88" s="21" t="str">
-        <f>IF(D88="","",LEN(D88))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5280,11 +5245,11 @@
         <v/>
       </c>
       <c r="R89" s="21" t="str">
-        <f>IF(C89="","",LEN(C89))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S89" s="21" t="str">
-        <f>IF(D89="","",LEN(D89))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5298,11 +5263,11 @@
         <v/>
       </c>
       <c r="R90" s="21" t="str">
-        <f>IF(C90="","",LEN(C90))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S90" s="21" t="str">
-        <f>IF(D90="","",LEN(D90))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5316,11 +5281,11 @@
         <v/>
       </c>
       <c r="R91" s="21" t="str">
-        <f>IF(C91="","",LEN(C91))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S91" s="21" t="str">
-        <f>IF(D91="","",LEN(D91))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5334,11 +5299,11 @@
         <v/>
       </c>
       <c r="R92" s="21" t="str">
-        <f>IF(C92="","",LEN(C92))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S92" s="21" t="str">
-        <f>IF(D92="","",LEN(D92))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5352,11 +5317,11 @@
         <v/>
       </c>
       <c r="R93" s="21" t="str">
-        <f>IF(C93="","",LEN(C93))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S93" s="21" t="str">
-        <f>IF(D93="","",LEN(D93))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5370,11 +5335,11 @@
         <v/>
       </c>
       <c r="R94" s="21" t="str">
-        <f>IF(C94="","",LEN(C94))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S94" s="21" t="str">
-        <f>IF(D94="","",LEN(D94))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5388,11 +5353,11 @@
         <v/>
       </c>
       <c r="R95" s="21" t="str">
-        <f>IF(C95="","",LEN(C95))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S95" s="21" t="str">
-        <f>IF(D95="","",LEN(D95))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5406,11 +5371,11 @@
         <v/>
       </c>
       <c r="R96" s="21" t="str">
-        <f>IF(C96="","",LEN(C96))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S96" s="21" t="str">
-        <f>IF(D96="","",LEN(D96))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5424,11 +5389,11 @@
         <v/>
       </c>
       <c r="R97" s="21" t="str">
-        <f>IF(C97="","",LEN(C97))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S97" s="21" t="str">
-        <f>IF(D97="","",LEN(D97))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5442,11 +5407,11 @@
         <v/>
       </c>
       <c r="R98" s="21" t="str">
-        <f>IF(C98="","",LEN(C98))</f>
+        <f t="shared" ref="R98:R129" si="6">IF(C98="","",LEN(C98))</f>
         <v/>
       </c>
       <c r="S98" s="21" t="str">
-        <f>IF(D98="","",LEN(D98))</f>
+        <f t="shared" ref="S98:S129" si="7">IF(D98="","",LEN(D98))</f>
         <v/>
       </c>
     </row>
@@ -5460,11 +5425,11 @@
         <v/>
       </c>
       <c r="R99" s="21" t="str">
-        <f>IF(C99="","",LEN(C99))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S99" s="21" t="str">
-        <f>IF(D99="","",LEN(D99))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5478,11 +5443,11 @@
         <v/>
       </c>
       <c r="R100" s="21" t="str">
-        <f>IF(C100="","",LEN(C100))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S100" s="21" t="str">
-        <f>IF(D100="","",LEN(D100))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5496,11 +5461,11 @@
         <v/>
       </c>
       <c r="R101" s="21" t="str">
-        <f>IF(C101="","",LEN(C101))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S101" s="21" t="str">
-        <f>IF(D101="","",LEN(D101))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5514,11 +5479,11 @@
         <v/>
       </c>
       <c r="R102" s="21" t="str">
-        <f>IF(C102="","",LEN(C102))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S102" s="21" t="str">
-        <f>IF(D102="","",LEN(D102))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5532,11 +5497,11 @@
         <v/>
       </c>
       <c r="R103" s="21" t="str">
-        <f>IF(C103="","",LEN(C103))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S103" s="21" t="str">
-        <f>IF(D103="","",LEN(D103))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5550,11 +5515,11 @@
         <v/>
       </c>
       <c r="R104" s="21" t="str">
-        <f>IF(C104="","",LEN(C104))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S104" s="21" t="str">
-        <f>IF(D104="","",LEN(D104))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5568,11 +5533,11 @@
         <v/>
       </c>
       <c r="R105" s="21" t="str">
-        <f>IF(C105="","",LEN(C105))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S105" s="21" t="str">
-        <f>IF(D105="","",LEN(D105))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5586,11 +5551,11 @@
         <v/>
       </c>
       <c r="R106" s="21" t="str">
-        <f>IF(C106="","",LEN(C106))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S106" s="21" t="str">
-        <f>IF(D106="","",LEN(D106))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5604,11 +5569,11 @@
         <v/>
       </c>
       <c r="R107" s="21" t="str">
-        <f>IF(C107="","",LEN(C107))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S107" s="21" t="str">
-        <f>IF(D107="","",LEN(D107))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5622,11 +5587,11 @@
         <v/>
       </c>
       <c r="R108" s="21" t="str">
-        <f>IF(C108="","",LEN(C108))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S108" s="21" t="str">
-        <f>IF(D108="","",LEN(D108))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5640,11 +5605,11 @@
         <v/>
       </c>
       <c r="R109" s="21" t="str">
-        <f>IF(C109="","",LEN(C109))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S109" s="21" t="str">
-        <f>IF(D109="","",LEN(D109))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5658,11 +5623,11 @@
         <v/>
       </c>
       <c r="R110" s="21" t="str">
-        <f>IF(C110="","",LEN(C110))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S110" s="21" t="str">
-        <f>IF(D110="","",LEN(D110))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5676,11 +5641,11 @@
         <v/>
       </c>
       <c r="R111" s="21" t="str">
-        <f>IF(C111="","",LEN(C111))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S111" s="21" t="str">
-        <f>IF(D111="","",LEN(D111))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5694,11 +5659,11 @@
         <v/>
       </c>
       <c r="R112" s="21" t="str">
-        <f>IF(C112="","",LEN(C112))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S112" s="21" t="str">
-        <f>IF(D112="","",LEN(D112))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5712,11 +5677,11 @@
         <v/>
       </c>
       <c r="R113" s="21" t="str">
-        <f>IF(C113="","",LEN(C113))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S113" s="21" t="str">
-        <f>IF(D113="","",LEN(D113))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5730,11 +5695,11 @@
         <v/>
       </c>
       <c r="R114" s="21" t="str">
-        <f>IF(C114="","",LEN(C114))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S114" s="21" t="str">
-        <f>IF(D114="","",LEN(D114))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5748,11 +5713,11 @@
         <v/>
       </c>
       <c r="R115" s="21" t="str">
-        <f>IF(C115="","",LEN(C115))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S115" s="21" t="str">
-        <f>IF(D115="","",LEN(D115))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5766,11 +5731,11 @@
         <v/>
       </c>
       <c r="R116" s="21" t="str">
-        <f>IF(C116="","",LEN(C116))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S116" s="21" t="str">
-        <f>IF(D116="","",LEN(D116))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5784,11 +5749,11 @@
         <v/>
       </c>
       <c r="R117" s="21" t="str">
-        <f>IF(C117="","",LEN(C117))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S117" s="21" t="str">
-        <f>IF(D117="","",LEN(D117))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5802,11 +5767,11 @@
         <v/>
       </c>
       <c r="R118" s="21" t="str">
-        <f>IF(C118="","",LEN(C118))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S118" s="21" t="str">
-        <f>IF(D118="","",LEN(D118))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5820,11 +5785,11 @@
         <v/>
       </c>
       <c r="R119" s="21" t="str">
-        <f>IF(C119="","",LEN(C119))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S119" s="21" t="str">
-        <f>IF(D119="","",LEN(D119))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5838,11 +5803,11 @@
         <v/>
       </c>
       <c r="R120" s="21" t="str">
-        <f>IF(C120="","",LEN(C120))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S120" s="21" t="str">
-        <f>IF(D120="","",LEN(D120))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5856,11 +5821,11 @@
         <v/>
       </c>
       <c r="R121" s="21" t="str">
-        <f>IF(C121="","",LEN(C121))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S121" s="21" t="str">
-        <f>IF(D121="","",LEN(D121))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5874,11 +5839,11 @@
         <v/>
       </c>
       <c r="R122" s="21" t="str">
-        <f>IF(C122="","",LEN(C122))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S122" s="21" t="str">
-        <f>IF(D122="","",LEN(D122))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5892,11 +5857,11 @@
         <v/>
       </c>
       <c r="R123" s="21" t="str">
-        <f>IF(C123="","",LEN(C123))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S123" s="21" t="str">
-        <f>IF(D123="","",LEN(D123))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5910,11 +5875,11 @@
         <v/>
       </c>
       <c r="R124" s="21" t="str">
-        <f>IF(C124="","",LEN(C124))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S124" s="21" t="str">
-        <f>IF(D124="","",LEN(D124))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5928,11 +5893,11 @@
         <v/>
       </c>
       <c r="R125" s="21" t="str">
-        <f>IF(C125="","",LEN(C125))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S125" s="21" t="str">
-        <f>IF(D125="","",LEN(D125))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5946,11 +5911,11 @@
         <v/>
       </c>
       <c r="R126" s="21" t="str">
-        <f>IF(C126="","",LEN(C126))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S126" s="21" t="str">
-        <f>IF(D126="","",LEN(D126))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5964,11 +5929,11 @@
         <v/>
       </c>
       <c r="R127" s="21" t="str">
-        <f>IF(C127="","",LEN(C127))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S127" s="21" t="str">
-        <f>IF(D127="","",LEN(D127))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5982,11 +5947,11 @@
         <v/>
       </c>
       <c r="R128" s="21" t="str">
-        <f>IF(C128="","",LEN(C128))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S128" s="21" t="str">
-        <f>IF(D128="","",LEN(D128))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6000,11 +5965,11 @@
         <v/>
       </c>
       <c r="R129" s="21" t="str">
-        <f>IF(C129="","",LEN(C129))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S129" s="21" t="str">
-        <f>IF(D129="","",LEN(D129))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6018,11 +5983,11 @@
         <v/>
       </c>
       <c r="R130" s="21" t="str">
-        <f>IF(C130="","",LEN(C130))</f>
+        <f t="shared" ref="R130:R161" si="8">IF(C130="","",LEN(C130))</f>
         <v/>
       </c>
       <c r="S130" s="21" t="str">
-        <f>IF(D130="","",LEN(D130))</f>
+        <f t="shared" ref="S130:S161" si="9">IF(D130="","",LEN(D130))</f>
         <v/>
       </c>
     </row>
@@ -6036,11 +6001,11 @@
         <v/>
       </c>
       <c r="R131" s="21" t="str">
-        <f>IF(C131="","",LEN(C131))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S131" s="21" t="str">
-        <f>IF(D131="","",LEN(D131))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6054,11 +6019,11 @@
         <v/>
       </c>
       <c r="R132" s="21" t="str">
-        <f>IF(C132="","",LEN(C132))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S132" s="21" t="str">
-        <f>IF(D132="","",LEN(D132))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6072,11 +6037,11 @@
         <v/>
       </c>
       <c r="R133" s="21" t="str">
-        <f>IF(C133="","",LEN(C133))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S133" s="21" t="str">
-        <f>IF(D133="","",LEN(D133))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6090,11 +6055,11 @@
         <v/>
       </c>
       <c r="R134" s="21" t="str">
-        <f>IF(C134="","",LEN(C134))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S134" s="21" t="str">
-        <f>IF(D134="","",LEN(D134))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6108,11 +6073,11 @@
         <v/>
       </c>
       <c r="R135" s="21" t="str">
-        <f>IF(C135="","",LEN(C135))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S135" s="21" t="str">
-        <f>IF(D135="","",LEN(D135))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6126,11 +6091,11 @@
         <v/>
       </c>
       <c r="R136" s="21" t="str">
-        <f>IF(C136="","",LEN(C136))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S136" s="21" t="str">
-        <f>IF(D136="","",LEN(D136))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6144,11 +6109,11 @@
         <v/>
       </c>
       <c r="R137" s="21" t="str">
-        <f>IF(C137="","",LEN(C137))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S137" s="21" t="str">
-        <f>IF(D137="","",LEN(D137))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6162,11 +6127,11 @@
         <v/>
       </c>
       <c r="R138" s="21" t="str">
-        <f>IF(C138="","",LEN(C138))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S138" s="21" t="str">
-        <f>IF(D138="","",LEN(D138))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6180,11 +6145,11 @@
         <v/>
       </c>
       <c r="R139" s="21" t="str">
-        <f>IF(C139="","",LEN(C139))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S139" s="21" t="str">
-        <f>IF(D139="","",LEN(D139))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6198,11 +6163,11 @@
         <v/>
       </c>
       <c r="R140" s="21" t="str">
-        <f>IF(C140="","",LEN(C140))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S140" s="21" t="str">
-        <f>IF(D140="","",LEN(D140))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6216,11 +6181,11 @@
         <v/>
       </c>
       <c r="R141" s="21" t="str">
-        <f>IF(C141="","",LEN(C141))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S141" s="21" t="str">
-        <f>IF(D141="","",LEN(D141))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6234,11 +6199,11 @@
         <v/>
       </c>
       <c r="R142" s="21" t="str">
-        <f>IF(C142="","",LEN(C142))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S142" s="21" t="str">
-        <f>IF(D142="","",LEN(D142))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6252,11 +6217,11 @@
         <v/>
       </c>
       <c r="R143" s="21" t="str">
-        <f>IF(C143="","",LEN(C143))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S143" s="21" t="str">
-        <f>IF(D143="","",LEN(D143))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6270,11 +6235,11 @@
         <v/>
       </c>
       <c r="R144" s="21" t="str">
-        <f>IF(C144="","",LEN(C144))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S144" s="21" t="str">
-        <f>IF(D144="","",LEN(D144))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6288,11 +6253,11 @@
         <v/>
       </c>
       <c r="R145" s="21" t="str">
-        <f>IF(C145="","",LEN(C145))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S145" s="21" t="str">
-        <f>IF(D145="","",LEN(D145))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6306,11 +6271,11 @@
         <v/>
       </c>
       <c r="R146" s="21" t="str">
-        <f>IF(C146="","",LEN(C146))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S146" s="21" t="str">
-        <f>IF(D146="","",LEN(D146))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6324,11 +6289,11 @@
         <v/>
       </c>
       <c r="R147" s="21" t="str">
-        <f>IF(C147="","",LEN(C147))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S147" s="21" t="str">
-        <f>IF(D147="","",LEN(D147))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6342,11 +6307,11 @@
         <v/>
       </c>
       <c r="R148" s="21" t="str">
-        <f>IF(C148="","",LEN(C148))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S148" s="21" t="str">
-        <f>IF(D148="","",LEN(D148))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6360,11 +6325,11 @@
         <v/>
       </c>
       <c r="R149" s="21" t="str">
-        <f>IF(C149="","",LEN(C149))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S149" s="21" t="str">
-        <f>IF(D149="","",LEN(D149))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6378,11 +6343,11 @@
         <v/>
       </c>
       <c r="R150" s="21" t="str">
-        <f>IF(C150="","",LEN(C150))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S150" s="21" t="str">
-        <f>IF(D150="","",LEN(D150))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6396,11 +6361,11 @@
         <v/>
       </c>
       <c r="R151" s="21" t="str">
-        <f>IF(C151="","",LEN(C151))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S151" s="21" t="str">
-        <f>IF(D151="","",LEN(D151))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6414,11 +6379,11 @@
         <v/>
       </c>
       <c r="R152" s="21" t="str">
-        <f>IF(C152="","",LEN(C152))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S152" s="21" t="str">
-        <f>IF(D152="","",LEN(D152))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6432,11 +6397,11 @@
         <v/>
       </c>
       <c r="R153" s="21" t="str">
-        <f>IF(C153="","",LEN(C153))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S153" s="21" t="str">
-        <f>IF(D153="","",LEN(D153))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6450,11 +6415,11 @@
         <v/>
       </c>
       <c r="R154" s="21" t="str">
-        <f>IF(C154="","",LEN(C154))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S154" s="21" t="str">
-        <f>IF(D154="","",LEN(D154))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6468,11 +6433,11 @@
         <v/>
       </c>
       <c r="R155" s="21" t="str">
-        <f>IF(C155="","",LEN(C155))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S155" s="21" t="str">
-        <f>IF(D155="","",LEN(D155))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6486,11 +6451,11 @@
         <v/>
       </c>
       <c r="R156" s="21" t="str">
-        <f>IF(C156="","",LEN(C156))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S156" s="21" t="str">
-        <f>IF(D156="","",LEN(D156))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6504,11 +6469,11 @@
         <v/>
       </c>
       <c r="R157" s="21" t="str">
-        <f>IF(C157="","",LEN(C157))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S157" s="21" t="str">
-        <f>IF(D157="","",LEN(D157))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6522,11 +6487,11 @@
         <v/>
       </c>
       <c r="R158" s="21" t="str">
-        <f>IF(C158="","",LEN(C158))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S158" s="21" t="str">
-        <f>IF(D158="","",LEN(D158))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6540,11 +6505,11 @@
         <v/>
       </c>
       <c r="R159" s="21" t="str">
-        <f>IF(C159="","",LEN(C159))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S159" s="21" t="str">
-        <f>IF(D159="","",LEN(D159))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6558,11 +6523,11 @@
         <v/>
       </c>
       <c r="R160" s="21" t="str">
-        <f>IF(C160="","",LEN(C160))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S160" s="21" t="str">
-        <f>IF(D160="","",LEN(D160))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6576,11 +6541,11 @@
         <v/>
       </c>
       <c r="R161" s="21" t="str">
-        <f>IF(C161="","",LEN(C161))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="S161" s="21" t="str">
-        <f>IF(D161="","",LEN(D161))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6594,11 +6559,11 @@
         <v/>
       </c>
       <c r="R162" s="21" t="str">
-        <f>IF(C162="","",LEN(C162))</f>
+        <f t="shared" ref="R162:R193" si="10">IF(C162="","",LEN(C162))</f>
         <v/>
       </c>
       <c r="S162" s="21" t="str">
-        <f>IF(D162="","",LEN(D162))</f>
+        <f t="shared" ref="S162:S193" si="11">IF(D162="","",LEN(D162))</f>
         <v/>
       </c>
     </row>
@@ -6612,11 +6577,11 @@
         <v/>
       </c>
       <c r="R163" s="21" t="str">
-        <f>IF(C163="","",LEN(C163))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S163" s="21" t="str">
-        <f>IF(D163="","",LEN(D163))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6630,11 +6595,11 @@
         <v/>
       </c>
       <c r="R164" s="21" t="str">
-        <f>IF(C164="","",LEN(C164))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S164" s="21" t="str">
-        <f>IF(D164="","",LEN(D164))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6648,11 +6613,11 @@
         <v/>
       </c>
       <c r="R165" s="21" t="str">
-        <f>IF(C165="","",LEN(C165))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S165" s="21" t="str">
-        <f>IF(D165="","",LEN(D165))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6666,11 +6631,11 @@
         <v/>
       </c>
       <c r="R166" s="21" t="str">
-        <f>IF(C166="","",LEN(C166))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S166" s="21" t="str">
-        <f>IF(D166="","",LEN(D166))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6684,11 +6649,11 @@
         <v/>
       </c>
       <c r="R167" s="21" t="str">
-        <f>IF(C167="","",LEN(C167))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S167" s="21" t="str">
-        <f>IF(D167="","",LEN(D167))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6702,11 +6667,11 @@
         <v/>
       </c>
       <c r="R168" s="21" t="str">
-        <f>IF(C168="","",LEN(C168))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S168" s="21" t="str">
-        <f>IF(D168="","",LEN(D168))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6720,11 +6685,11 @@
         <v/>
       </c>
       <c r="R169" s="21" t="str">
-        <f>IF(C169="","",LEN(C169))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S169" s="21" t="str">
-        <f>IF(D169="","",LEN(D169))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6738,11 +6703,11 @@
         <v/>
       </c>
       <c r="R170" s="21" t="str">
-        <f>IF(C170="","",LEN(C170))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S170" s="21" t="str">
-        <f>IF(D170="","",LEN(D170))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6756,11 +6721,11 @@
         <v/>
       </c>
       <c r="R171" s="21" t="str">
-        <f>IF(C171="","",LEN(C171))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S171" s="21" t="str">
-        <f>IF(D171="","",LEN(D171))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6774,11 +6739,11 @@
         <v/>
       </c>
       <c r="R172" s="21" t="str">
-        <f>IF(C172="","",LEN(C172))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S172" s="21" t="str">
-        <f>IF(D172="","",LEN(D172))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6792,11 +6757,11 @@
         <v/>
       </c>
       <c r="R173" s="21" t="str">
-        <f>IF(C173="","",LEN(C173))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S173" s="21" t="str">
-        <f>IF(D173="","",LEN(D173))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6810,11 +6775,11 @@
         <v/>
       </c>
       <c r="R174" s="21" t="str">
-        <f>IF(C174="","",LEN(C174))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S174" s="21" t="str">
-        <f>IF(D174="","",LEN(D174))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6828,11 +6793,11 @@
         <v/>
       </c>
       <c r="R175" s="21" t="str">
-        <f>IF(C175="","",LEN(C175))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S175" s="21" t="str">
-        <f>IF(D175="","",LEN(D175))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6846,11 +6811,11 @@
         <v/>
       </c>
       <c r="R176" s="21" t="str">
-        <f>IF(C176="","",LEN(C176))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S176" s="21" t="str">
-        <f>IF(D176="","",LEN(D176))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6864,11 +6829,11 @@
         <v/>
       </c>
       <c r="R177" s="21" t="str">
-        <f>IF(C177="","",LEN(C177))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S177" s="21" t="str">
-        <f>IF(D177="","",LEN(D177))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6882,11 +6847,11 @@
         <v/>
       </c>
       <c r="R178" s="21" t="str">
-        <f>IF(C178="","",LEN(C178))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S178" s="21" t="str">
-        <f>IF(D178="","",LEN(D178))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6900,11 +6865,11 @@
         <v/>
       </c>
       <c r="R179" s="21" t="str">
-        <f>IF(C179="","",LEN(C179))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S179" s="21" t="str">
-        <f>IF(D179="","",LEN(D179))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6918,11 +6883,11 @@
         <v/>
       </c>
       <c r="R180" s="21" t="str">
-        <f>IF(C180="","",LEN(C180))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S180" s="21" t="str">
-        <f>IF(D180="","",LEN(D180))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6936,11 +6901,11 @@
         <v/>
       </c>
       <c r="R181" s="21" t="str">
-        <f>IF(C181="","",LEN(C181))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S181" s="21" t="str">
-        <f>IF(D181="","",LEN(D181))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6954,11 +6919,11 @@
         <v/>
       </c>
       <c r="R182" s="21" t="str">
-        <f>IF(C182="","",LEN(C182))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S182" s="21" t="str">
-        <f>IF(D182="","",LEN(D182))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6972,11 +6937,11 @@
         <v/>
       </c>
       <c r="R183" s="21" t="str">
-        <f>IF(C183="","",LEN(C183))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S183" s="21" t="str">
-        <f>IF(D183="","",LEN(D183))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6990,11 +6955,11 @@
         <v/>
       </c>
       <c r="R184" s="21" t="str">
-        <f>IF(C184="","",LEN(C184))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S184" s="21" t="str">
-        <f>IF(D184="","",LEN(D184))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -7008,11 +6973,11 @@
         <v/>
       </c>
       <c r="R185" s="21" t="str">
-        <f>IF(C185="","",LEN(C185))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S185" s="21" t="str">
-        <f>IF(D185="","",LEN(D185))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -7026,11 +6991,11 @@
         <v/>
       </c>
       <c r="R186" s="21" t="str">
-        <f>IF(C186="","",LEN(C186))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S186" s="21" t="str">
-        <f>IF(D186="","",LEN(D186))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -7044,11 +7009,11 @@
         <v/>
       </c>
       <c r="R187" s="21" t="str">
-        <f>IF(C187="","",LEN(C187))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S187" s="21" t="str">
-        <f>IF(D187="","",LEN(D187))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -7062,11 +7027,11 @@
         <v/>
       </c>
       <c r="R188" s="21" t="str">
-        <f>IF(C188="","",LEN(C188))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S188" s="21" t="str">
-        <f>IF(D188="","",LEN(D188))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -7080,11 +7045,11 @@
         <v/>
       </c>
       <c r="R189" s="21" t="str">
-        <f>IF(C189="","",LEN(C189))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S189" s="21" t="str">
-        <f>IF(D189="","",LEN(D189))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -7098,11 +7063,11 @@
         <v/>
       </c>
       <c r="R190" s="21" t="str">
-        <f>IF(C190="","",LEN(C190))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S190" s="21" t="str">
-        <f>IF(D190="","",LEN(D190))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -7116,11 +7081,11 @@
         <v/>
       </c>
       <c r="R191" s="21" t="str">
-        <f>IF(C191="","",LEN(C191))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S191" s="21" t="str">
-        <f>IF(D191="","",LEN(D191))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -7134,11 +7099,11 @@
         <v/>
       </c>
       <c r="R192" s="21" t="str">
-        <f>IF(C192="","",LEN(C192))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S192" s="21" t="str">
-        <f>IF(D192="","",LEN(D192))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -7152,11 +7117,11 @@
         <v/>
       </c>
       <c r="R193" s="21" t="str">
-        <f>IF(C193="","",LEN(C193))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="S193" s="21" t="str">
-        <f>IF(D193="","",LEN(D193))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -7170,11 +7135,11 @@
         <v/>
       </c>
       <c r="R194" s="21" t="str">
-        <f>IF(C194="","",LEN(C194))</f>
+        <f t="shared" ref="R194:R200" si="12">IF(C194="","",LEN(C194))</f>
         <v/>
       </c>
       <c r="S194" s="21" t="str">
-        <f>IF(D194="","",LEN(D194))</f>
+        <f t="shared" ref="S194:S200" si="13">IF(D194="","",LEN(D194))</f>
         <v/>
       </c>
     </row>
@@ -7188,11 +7153,11 @@
         <v/>
       </c>
       <c r="R195" s="21" t="str">
-        <f>IF(C195="","",LEN(C195))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S195" s="21" t="str">
-        <f>IF(D195="","",LEN(D195))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -7206,11 +7171,11 @@
         <v/>
       </c>
       <c r="R196" s="21" t="str">
-        <f>IF(C196="","",LEN(C196))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S196" s="21" t="str">
-        <f>IF(D196="","",LEN(D196))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -7224,11 +7189,11 @@
         <v/>
       </c>
       <c r="R197" s="21" t="str">
-        <f>IF(C197="","",LEN(C197))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S197" s="21" t="str">
-        <f>IF(D197="","",LEN(D197))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -7242,11 +7207,11 @@
         <v/>
       </c>
       <c r="R198" s="21" t="str">
-        <f>IF(C198="","",LEN(C198))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S198" s="21" t="str">
-        <f>IF(D198="","",LEN(D198))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -7260,11 +7225,11 @@
         <v/>
       </c>
       <c r="R199" s="21" t="str">
-        <f>IF(C199="","",LEN(C199))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S199" s="21" t="str">
-        <f>IF(D199="","",LEN(D199))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -7278,23 +7243,23 @@
         <v/>
       </c>
       <c r="R200" s="21" t="str">
-        <f>IF(C200="","",LEN(C200))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S200" s="21" t="str">
-        <f>IF(D200="","",LEN(D200))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0"/>
   <conditionalFormatting sqref="C2:C200">
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>LEN(C2)&gt;40</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D200">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>LEN(D2)&gt;30</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7302,8 +7267,6 @@
     <cfRule type="expression" dxfId="3" priority="5">
       <formula>AND(ISNUMBER(R2),R2&gt;40)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R200">
     <cfRule type="expression" dxfId="2" priority="6">
       <formula>AND(ISNUMBER(R2),R2&lt;=40)</formula>
     </cfRule>
@@ -7312,8 +7275,6 @@
     <cfRule type="expression" dxfId="1" priority="7">
       <formula>AND(ISNUMBER(S2),S2&gt;30)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S200">
     <cfRule type="expression" dxfId="0" priority="8">
       <formula>AND(ISNUMBER(S2),S2&lt;=30)</formula>
     </cfRule>
@@ -7403,1016 +7364,1012 @@
   <dimension ref="A1:AG40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" style="25" customWidth="1"/>
-    <col min="2" max="2" width="12" style="25" customWidth="1"/>
-    <col min="3" max="3" width="3" style="25" customWidth="1"/>
-    <col min="4" max="4" width="22" style="25" customWidth="1"/>
-    <col min="5" max="5" width="12" style="25" customWidth="1"/>
-    <col min="6" max="6" width="3" style="25" customWidth="1"/>
-    <col min="7" max="7" width="24" style="25" customWidth="1"/>
-    <col min="8" max="8" width="14" style="25" customWidth="1"/>
-    <col min="9" max="9" width="3" style="25" customWidth="1"/>
-    <col min="10" max="10" width="10" style="25" customWidth="1"/>
-    <col min="11" max="11" width="3" style="25" customWidth="1"/>
-    <col min="12" max="12" width="14" style="25" customWidth="1"/>
-    <col min="13" max="13" width="3" style="25" customWidth="1"/>
-    <col min="14" max="15" width="22" style="25" customWidth="1"/>
-    <col min="16" max="16" width="2.42578125" style="25" customWidth="1"/>
-    <col min="17" max="17" width="24" style="25" customWidth="1"/>
-    <col min="18" max="18" width="3" style="25" customWidth="1"/>
-    <col min="19" max="19" width="28" style="25" customWidth="1"/>
-    <col min="20" max="20" width="3" style="25" customWidth="1"/>
-    <col min="21" max="21" width="12" style="25" customWidth="1"/>
-    <col min="22" max="22" width="8.7109375" style="25"/>
-    <col min="23" max="23" width="22" style="25" customWidth="1"/>
-    <col min="24" max="24" width="12" style="25" customWidth="1"/>
-    <col min="25" max="25" width="40" style="25" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" style="25"/>
-    <col min="27" max="27" width="24" style="25" customWidth="1"/>
-    <col min="28" max="28" width="48" style="25" customWidth="1"/>
-    <col min="29" max="29" width="34" style="25" customWidth="1"/>
-    <col min="30" max="30" width="40" style="25" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" style="25"/>
-    <col min="32" max="32" width="43" style="25" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="8.7109375" style="25"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="3" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="3" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="3" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="3" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="3" customWidth="1"/>
+    <col min="14" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="2.42578125" customWidth="1"/>
+    <col min="17" max="17" width="24" customWidth="1"/>
+    <col min="18" max="18" width="3" customWidth="1"/>
+    <col min="19" max="19" width="28" customWidth="1"/>
+    <col min="20" max="20" width="3" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="23" max="23" width="22" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="40" customWidth="1"/>
+    <col min="27" max="27" width="24" customWidth="1"/>
+    <col min="28" max="28" width="48" customWidth="1"/>
+    <col min="29" max="29" width="34" customWidth="1"/>
+    <col min="30" max="30" width="40" customWidth="1"/>
+    <col min="32" max="32" width="43" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>755</v>
       </c>
-      <c r="W1" s="26" t="s">
+      <c r="W1" s="25" t="s">
         <v>821</v>
       </c>
-      <c r="AA1" s="27" t="s">
+      <c r="AA1" s="26" t="s">
         <v>858</v>
       </c>
-      <c r="AF1" s="26" t="s">
+      <c r="AF1" s="25" t="s">
         <v>922</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="W2" s="28" t="s">
+      <c r="W2" s="39" t="s">
         <v>822</v>
       </c>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="AA2" s="29" t="s">
+      <c r="X2" s="39"/>
+      <c r="Y2" s="39"/>
+      <c r="AA2" s="27" t="s">
         <v>859</v>
       </c>
-      <c r="AF2" s="28" t="s">
+      <c r="AF2" s="39" t="s">
         <v>923</v>
       </c>
-      <c r="AG2" s="28"/>
+      <c r="AG2" s="39"/>
     </row>
     <row r="3" spans="1:33" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>756</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="28" t="s">
         <v>757</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="28" t="s">
         <v>758</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="28" t="s">
         <v>757</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="28" t="s">
         <v>759</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="28" t="s">
         <v>757</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="J3" s="28" t="s">
         <v>760</v>
       </c>
-      <c r="L3" s="30" t="s">
+      <c r="L3" s="28" t="s">
         <v>761</v>
       </c>
-      <c r="N3" s="30" t="s">
+      <c r="N3" s="28" t="s">
         <v>762</v>
       </c>
-      <c r="O3" s="31"/>
-      <c r="Q3" s="30" t="s">
+      <c r="O3" s="29"/>
+      <c r="Q3" s="28" t="s">
         <v>763</v>
       </c>
-      <c r="S3" s="30" t="s">
+      <c r="S3" s="28" t="s">
         <v>764</v>
       </c>
-      <c r="U3" s="30" t="s">
+      <c r="U3" s="28" t="s">
         <v>765</v>
       </c>
-      <c r="W3" s="30" t="s">
+      <c r="W3" s="28" t="s">
         <v>823</v>
       </c>
-      <c r="X3" s="30" t="s">
+      <c r="X3" s="28" t="s">
         <v>824</v>
       </c>
-      <c r="Y3" s="30" t="s">
+      <c r="Y3" s="28" t="s">
         <v>825</v>
       </c>
-      <c r="AF3" s="30" t="s">
+      <c r="AF3" s="28" t="s">
         <v>924</v>
       </c>
-      <c r="AG3" s="30" t="s">
+      <c r="AG3" s="28" t="s">
         <v>925</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="30" t="s">
         <v>766</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="30" t="s">
         <v>767</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="30" t="s">
         <v>768</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="30" t="s">
         <v>769</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="30" t="s">
         <v>770</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="L4" s="30" t="s">
         <v>433</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="O4" s="33" t="s">
+      <c r="O4" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="Q4" s="32" t="s">
+      <c r="Q4" s="30" t="s">
         <v>771</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="S4" s="30" t="s">
         <v>772</v>
       </c>
-      <c r="U4" s="32">
+      <c r="U4" s="30">
         <v>1</v>
       </c>
-      <c r="W4" s="34" t="s">
+      <c r="W4" s="31" t="s">
         <v>826</v>
       </c>
-      <c r="X4" s="34" t="s">
+      <c r="X4" s="31" t="s">
         <v>827</v>
       </c>
-      <c r="Y4" s="32" t="s">
+      <c r="Y4" s="30" t="s">
         <v>828</v>
       </c>
-      <c r="AA4" s="35" t="s">
+      <c r="AA4" s="32" t="s">
         <v>860</v>
       </c>
-      <c r="AF4" s="34" t="s">
+      <c r="AF4" s="31" t="s">
         <v>694</v>
       </c>
-      <c r="AG4" s="34" t="s">
+      <c r="AG4" s="31" t="s">
         <v>914</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="30" t="s">
         <v>774</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="30" t="s">
         <v>775</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="30" t="s">
         <v>776</v>
       </c>
-      <c r="J5" s="32" t="s">
+      <c r="J5" s="30" t="s">
         <v>777</v>
       </c>
-      <c r="L5" s="32" t="s">
+      <c r="L5" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="N5" s="33" t="s">
+      <c r="N5" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="O5" s="33" t="s">
+      <c r="O5" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="Q5" s="32" t="s">
+      <c r="Q5" s="30" t="s">
         <v>778</v>
       </c>
-      <c r="S5" s="32" t="s">
+      <c r="S5" s="30" t="s">
         <v>779</v>
       </c>
-      <c r="U5" s="32">
+      <c r="U5" s="30">
         <v>2</v>
       </c>
-      <c r="W5" s="34" t="s">
+      <c r="W5" s="31" t="s">
         <v>829</v>
       </c>
-      <c r="X5" s="34" t="s">
+      <c r="X5" s="31" t="s">
         <v>830</v>
       </c>
-      <c r="Y5" s="32" t="s">
+      <c r="Y5" s="30" t="s">
         <v>831</v>
       </c>
-      <c r="AA5" s="30" t="s">
+      <c r="AA5" s="28" t="s">
         <v>761</v>
       </c>
-      <c r="AB5" s="30" t="s">
+      <c r="AB5" s="28" t="s">
         <v>861</v>
       </c>
-      <c r="AC5" s="30" t="s">
+      <c r="AC5" s="28" t="s">
         <v>862</v>
       </c>
-      <c r="AD5" s="30" t="s">
+      <c r="AD5" s="28" t="s">
         <v>863</v>
       </c>
-      <c r="AF5" s="34" t="s">
+      <c r="AF5" s="31" t="s">
         <v>548</v>
       </c>
-      <c r="AG5" s="34" t="s">
+      <c r="AG5" s="31" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="30" t="s">
         <v>905</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="33" t="s">
         <v>909</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="30" t="s">
         <v>780</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="30" t="s">
         <v>781</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="30" t="s">
         <v>782</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="30" t="s">
         <v>783</v>
       </c>
-      <c r="J6" s="32" t="s">
+      <c r="J6" s="30" t="s">
         <v>784</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="L6" s="30" t="s">
         <v>431</v>
       </c>
-      <c r="N6" s="33" t="s">
+      <c r="N6" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="O6" s="33" t="s">
+      <c r="O6" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="S6" s="32" t="s">
+      <c r="S6" s="30" t="s">
         <v>785</v>
       </c>
-      <c r="W6" s="34" t="s">
+      <c r="W6" s="31" t="s">
         <v>832</v>
       </c>
-      <c r="X6" s="34" t="s">
+      <c r="X6" s="31" t="s">
         <v>833</v>
       </c>
-      <c r="Y6" s="32" t="s">
+      <c r="Y6" s="30" t="s">
         <v>834</v>
       </c>
-      <c r="AA6" s="37" t="s">
+      <c r="AA6" s="34" t="s">
         <v>864</v>
       </c>
-      <c r="AB6" s="37" t="s">
+      <c r="AB6" s="34" t="s">
         <v>865</v>
       </c>
-      <c r="AC6" s="37" t="s">
+      <c r="AC6" s="34" t="s">
         <v>866</v>
       </c>
-      <c r="AD6" s="38" t="s">
+      <c r="AD6" s="35" t="s">
         <v>917</v>
       </c>
-      <c r="AF6" s="34" t="s">
+      <c r="AF6" s="31" t="s">
         <v>521</v>
       </c>
-      <c r="AG6" s="34" t="s">
+      <c r="AG6" s="31" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="30" t="s">
         <v>906</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="30" t="s">
         <v>792</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="30" t="s">
         <v>786</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="30" t="s">
         <v>787</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="H7" s="30" t="s">
         <v>788</v>
       </c>
-      <c r="J7" s="32" t="s">
+      <c r="J7" s="30" t="s">
         <v>789</v>
       </c>
-      <c r="L7" s="32" t="s">
+      <c r="L7" s="30" t="s">
         <v>437</v>
       </c>
-      <c r="N7" s="33" t="s">
+      <c r="N7" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="O7" s="33" t="s">
+      <c r="O7" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="S7" s="32" t="s">
+      <c r="S7" s="30" t="s">
         <v>791</v>
       </c>
-      <c r="W7" s="34" t="s">
+      <c r="W7" s="31" t="s">
         <v>835</v>
       </c>
-      <c r="X7" s="34" t="s">
+      <c r="X7" s="31" t="s">
         <v>836</v>
       </c>
-      <c r="Y7" s="32" t="s">
+      <c r="Y7" s="30" t="s">
         <v>837</v>
       </c>
-      <c r="AA7" s="37" t="s">
+      <c r="AA7" s="34" t="s">
         <v>867</v>
       </c>
-      <c r="AB7" s="37" t="s">
+      <c r="AB7" s="34" t="s">
         <v>868</v>
       </c>
-      <c r="AC7" s="37" t="s">
+      <c r="AC7" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="AD7" s="37" t="s">
+      <c r="AD7" s="34" t="s">
         <v>870</v>
       </c>
-      <c r="AF7" s="34" t="s">
+      <c r="AF7" s="31" t="s">
         <v>708</v>
       </c>
-      <c r="AG7" s="34" t="s">
+      <c r="AG7" s="31" t="s">
         <v>926</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="30" t="s">
         <v>907</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="30" t="s">
         <v>796</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="30" t="s">
         <v>793</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="30" t="s">
         <v>793</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="30" t="s">
         <v>794</v>
       </c>
-      <c r="N8" s="32"/>
-      <c r="O8" s="39"/>
-      <c r="S8" s="32" t="s">
+      <c r="N8" s="30"/>
+      <c r="O8" s="36"/>
+      <c r="S8" s="30" t="s">
         <v>795</v>
       </c>
-      <c r="W8" s="34" t="s">
+      <c r="W8" s="31" t="s">
         <v>838</v>
       </c>
-      <c r="X8" s="34" t="s">
+      <c r="X8" s="31" t="s">
         <v>839</v>
       </c>
-      <c r="Y8" s="32" t="s">
+      <c r="Y8" s="30" t="s">
         <v>840</v>
       </c>
-      <c r="AA8" s="38" t="s">
+      <c r="AA8" s="35" t="s">
         <v>915</v>
       </c>
-      <c r="AB8" s="37" t="s">
+      <c r="AB8" s="34" t="s">
         <v>871</v>
       </c>
-      <c r="AC8" s="38" t="s">
+      <c r="AC8" s="35" t="s">
         <v>916</v>
       </c>
-      <c r="AD8" s="37" t="s">
+      <c r="AD8" s="34" t="s">
         <v>872</v>
       </c>
-      <c r="AF8" s="34" t="s">
+      <c r="AF8" s="31" t="s">
         <v>737</v>
       </c>
-      <c r="AG8" s="34" t="s">
+      <c r="AG8" s="31" t="s">
         <v>927</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="30" t="s">
         <v>908</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="30" t="s">
         <v>797</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="30" t="s">
         <v>798</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="30" t="s">
         <v>799</v>
       </c>
-      <c r="N9" s="32"/>
-      <c r="O9" s="39"/>
-      <c r="S9" s="32" t="s">
+      <c r="N9" s="30"/>
+      <c r="O9" s="36"/>
+      <c r="S9" s="30" t="s">
         <v>771</v>
       </c>
-      <c r="W9" s="34" t="s">
+      <c r="W9" s="31" t="s">
         <v>841</v>
       </c>
-      <c r="X9" s="34" t="s">
+      <c r="X9" s="31" t="s">
         <v>842</v>
       </c>
-      <c r="Y9" s="32" t="s">
+      <c r="Y9" s="30" t="s">
         <v>843</v>
       </c>
-      <c r="AA9" s="37" t="s">
+      <c r="AA9" s="34" t="s">
         <v>873</v>
       </c>
-      <c r="AB9" s="37" t="s">
+      <c r="AB9" s="34" t="s">
         <v>874</v>
       </c>
-      <c r="AC9" s="37" t="s">
+      <c r="AC9" s="34" t="s">
         <v>875</v>
       </c>
-      <c r="AD9" s="37" t="s">
+      <c r="AD9" s="34" t="s">
         <v>876</v>
       </c>
-      <c r="AF9" s="34" t="s">
+      <c r="AF9" s="31" t="s">
         <v>734</v>
       </c>
-      <c r="AG9" s="34" t="s">
+      <c r="AG9" s="31" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="30" t="s">
         <v>800</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" s="30" t="s">
         <v>801</v>
       </c>
-      <c r="N10" s="32"/>
-      <c r="O10" s="39"/>
-      <c r="S10" s="32" t="s">
+      <c r="N10" s="30"/>
+      <c r="O10" s="36"/>
+      <c r="S10" s="30" t="s">
         <v>778</v>
       </c>
-      <c r="W10" s="34" t="s">
+      <c r="W10" s="31" t="s">
         <v>844</v>
       </c>
-      <c r="X10" s="34" t="s">
+      <c r="X10" s="31" t="s">
         <v>845</v>
       </c>
-      <c r="Y10" s="32" t="s">
+      <c r="Y10" s="30" t="s">
         <v>846</v>
       </c>
-      <c r="AA10" s="37" t="s">
+      <c r="AA10" s="34" t="s">
         <v>877</v>
       </c>
-      <c r="AB10" s="37" t="s">
+      <c r="AB10" s="34" t="s">
         <v>878</v>
       </c>
-      <c r="AC10" s="37" t="s">
+      <c r="AC10" s="34" t="s">
         <v>879</v>
       </c>
-      <c r="AD10" s="37" t="s">
+      <c r="AD10" s="34" t="s">
         <v>880</v>
       </c>
-      <c r="AF10" s="34" t="s">
+      <c r="AF10" s="31" t="s">
         <v>685</v>
       </c>
-      <c r="AG10" s="34" t="s">
+      <c r="AG10" s="31" t="s">
         <v>929</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" s="30" t="s">
         <v>802</v>
       </c>
-      <c r="S11" s="32" t="s">
+      <c r="S11" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="W11" s="34" t="s">
+      <c r="W11" s="31" t="s">
         <v>847</v>
       </c>
-      <c r="X11" s="34" t="s">
+      <c r="X11" s="31" t="s">
         <v>848</v>
       </c>
-      <c r="Y11" s="32" t="s">
+      <c r="Y11" s="30" t="s">
         <v>846</v>
       </c>
-      <c r="AA11" s="37" t="s">
+      <c r="AA11" s="34" t="s">
         <v>881</v>
       </c>
-      <c r="AB11" s="37" t="s">
+      <c r="AB11" s="34" t="s">
         <v>882</v>
       </c>
-      <c r="AC11" s="37" t="s">
+      <c r="AC11" s="34" t="s">
         <v>883</v>
       </c>
-      <c r="AD11" s="37" t="s">
+      <c r="AD11" s="34" t="s">
         <v>884</v>
       </c>
-      <c r="AF11" s="34" t="s">
+      <c r="AF11" s="31" t="s">
         <v>703</v>
       </c>
-      <c r="AG11" s="34" t="s">
+      <c r="AG11" s="31" t="s">
         <v>930</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" s="30" t="s">
         <v>803</v>
       </c>
-      <c r="S12" s="32" t="s">
+      <c r="S12" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="W12" s="34" t="s">
+      <c r="W12" s="31" t="s">
         <v>849</v>
       </c>
-      <c r="X12" s="34" t="s">
+      <c r="X12" s="31" t="s">
         <v>850</v>
       </c>
-      <c r="Y12" s="32" t="s">
+      <c r="Y12" s="30" t="s">
         <v>851</v>
       </c>
-      <c r="AA12" s="37" t="s">
+      <c r="AA12" s="34" t="s">
         <v>885</v>
       </c>
-      <c r="AB12" s="37" t="s">
+      <c r="AB12" s="34" t="s">
         <v>886</v>
       </c>
-      <c r="AC12" s="37" t="s">
+      <c r="AC12" s="34" t="s">
         <v>790</v>
       </c>
-      <c r="AD12" s="37" t="s">
+      <c r="AD12" s="34" t="s">
         <v>887</v>
       </c>
-      <c r="AF12" s="34" t="s">
+      <c r="AF12" s="31" t="s">
         <v>712</v>
       </c>
-      <c r="AG12" s="34" t="s">
+      <c r="AG12" s="31" t="s">
         <v>931</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="H13" s="30" t="s">
         <v>804</v>
       </c>
-      <c r="S13" s="32" t="s">
+      <c r="S13" s="30" t="s">
         <v>782</v>
       </c>
-      <c r="W13" s="34" t="s">
+      <c r="W13" s="31" t="s">
         <v>852</v>
       </c>
-      <c r="X13" s="34" t="s">
+      <c r="X13" s="31" t="s">
         <v>853</v>
       </c>
-      <c r="Y13" s="32" t="s">
+      <c r="Y13" s="30" t="s">
         <v>854</v>
       </c>
-      <c r="AA13" s="37" t="s">
+      <c r="AA13" s="34" t="s">
         <v>888</v>
       </c>
-      <c r="AB13" s="37" t="s">
+      <c r="AB13" s="34" t="s">
         <v>889</v>
       </c>
-      <c r="AC13" s="37" t="s">
+      <c r="AC13" s="34" t="s">
         <v>890</v>
       </c>
-      <c r="AD13" s="37" t="s">
+      <c r="AD13" s="34" t="s">
         <v>891</v>
       </c>
-      <c r="AF13" s="34" t="s">
+      <c r="AF13" s="31" t="s">
         <v>714</v>
       </c>
-      <c r="AG13" s="34" t="s">
+      <c r="AG13" s="31" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="30" t="s">
         <v>805</v>
       </c>
-      <c r="S14" s="32" t="s">
+      <c r="S14" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="W14" s="34" t="s">
+      <c r="W14" s="31" t="s">
         <v>855</v>
       </c>
-      <c r="X14" s="34" t="s">
+      <c r="X14" s="31" t="s">
         <v>856</v>
       </c>
-      <c r="Y14" s="32" t="s">
+      <c r="Y14" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="AF14" s="34" t="s">
+      <c r="AF14" s="31" t="s">
         <v>724</v>
       </c>
-      <c r="AG14" s="34" t="s">
+      <c r="AG14" s="31" t="s">
         <v>932</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="30" t="s">
         <v>806</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="H15" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="S15" s="32" t="s">
+      <c r="S15" s="30" t="s">
         <v>793</v>
       </c>
-      <c r="W15" s="34"/>
-      <c r="X15" s="34"/>
-      <c r="Y15" s="32"/>
-      <c r="AA15" s="35" t="s">
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="30"/>
+      <c r="AA15" s="32" t="s">
         <v>892</v>
       </c>
-      <c r="AF15" s="34" t="s">
+      <c r="AF15" s="31" t="s">
         <v>732</v>
       </c>
-      <c r="AG15" s="34" t="s">
+      <c r="AG15" s="31" t="s">
         <v>732</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="30" t="s">
         <v>807</v>
       </c>
-      <c r="S16" s="32" t="s">
+      <c r="S16" s="30" t="s">
         <v>797</v>
       </c>
-      <c r="W16" s="34"/>
-      <c r="X16" s="34"/>
-      <c r="Y16" s="32"/>
-      <c r="AA16" s="40" t="s">
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="30"/>
+      <c r="AA16" s="38" t="s">
         <v>893</v>
       </c>
-      <c r="AB16" s="40"/>
-      <c r="AC16" s="40"/>
-      <c r="AD16" s="40"/>
-      <c r="AF16" s="34" t="s">
+      <c r="AB16" s="38"/>
+      <c r="AC16" s="38"/>
+      <c r="AD16" s="38"/>
+      <c r="AF16" s="31" t="s">
         <v>680</v>
       </c>
-      <c r="AG16" s="34" t="s">
+      <c r="AG16" s="31" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="17" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="30" t="s">
         <v>808</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="30" t="s">
         <v>809</v>
       </c>
-      <c r="S17" s="32" t="s">
+      <c r="S17" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="W17" s="34"/>
-      <c r="X17" s="34"/>
-      <c r="Y17" s="32"/>
-      <c r="AA17" s="40" t="s">
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="30"/>
+      <c r="AA17" s="38" t="s">
         <v>894</v>
       </c>
-      <c r="AB17" s="40"/>
-      <c r="AC17" s="40"/>
-      <c r="AD17" s="40"/>
-      <c r="AF17" s="34"/>
-      <c r="AG17" s="34"/>
+      <c r="AB17" s="38"/>
+      <c r="AC17" s="38"/>
+      <c r="AD17" s="38"/>
+      <c r="AF17" s="31"/>
+      <c r="AG17" s="31"/>
     </row>
     <row r="18" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="30" t="s">
         <v>810</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="30" t="s">
         <v>811</v>
       </c>
-      <c r="S18" s="32" t="s">
+      <c r="S18" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="W18" s="34"/>
-      <c r="X18" s="34"/>
-      <c r="Y18" s="32"/>
-      <c r="AA18" s="41" t="s">
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="30"/>
+      <c r="AA18" s="40" t="s">
         <v>918</v>
       </c>
-      <c r="AB18" s="40"/>
-      <c r="AC18" s="40"/>
-      <c r="AD18" s="40"/>
-      <c r="AF18" s="34"/>
-      <c r="AG18" s="34"/>
+      <c r="AB18" s="38"/>
+      <c r="AC18" s="38"/>
+      <c r="AD18" s="38"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="31"/>
     </row>
     <row r="19" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G19" s="32" t="s">
+      <c r="G19" s="30" t="s">
         <v>396</v>
       </c>
-      <c r="H19" s="32" t="s">
+      <c r="H19" s="30" t="s">
         <v>812</v>
       </c>
-      <c r="S19" s="32" t="s">
+      <c r="S19" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="W19" s="34"/>
-      <c r="X19" s="34"/>
-      <c r="Y19" s="32"/>
-      <c r="AF19" s="34"/>
-      <c r="AG19" s="34"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="30"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="31"/>
     </row>
     <row r="20" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="30" t="s">
         <v>813</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" s="30" t="s">
         <v>814</v>
       </c>
-      <c r="S20" s="32" t="s">
+      <c r="S20" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="W20" s="34"/>
-      <c r="X20" s="34"/>
-      <c r="Y20" s="32"/>
-      <c r="AA20" s="35" t="s">
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="30"/>
+      <c r="AA20" s="32" t="s">
         <v>895</v>
       </c>
-      <c r="AF20" s="34"/>
-      <c r="AG20" s="34"/>
+      <c r="AF20" s="31"/>
+      <c r="AG20" s="31"/>
     </row>
     <row r="21" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G21" s="32" t="s">
+      <c r="G21" s="30" t="s">
         <v>815</v>
       </c>
-      <c r="H21" s="32" t="s">
+      <c r="H21" s="30" t="s">
         <v>816</v>
       </c>
-      <c r="S21" s="32" t="s">
+      <c r="S21" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="W21" s="34"/>
-      <c r="X21" s="34"/>
-      <c r="Y21" s="32"/>
-      <c r="AA21" s="40" t="s">
+      <c r="W21" s="31"/>
+      <c r="X21" s="31"/>
+      <c r="Y21" s="30"/>
+      <c r="AA21" s="38" t="s">
         <v>896</v>
       </c>
-      <c r="AB21" s="40"/>
-      <c r="AC21" s="40"/>
-      <c r="AD21" s="40"/>
-      <c r="AF21" s="34"/>
-      <c r="AG21" s="34"/>
+      <c r="AB21" s="38"/>
+      <c r="AC21" s="38"/>
+      <c r="AD21" s="38"/>
+      <c r="AF21" s="31"/>
+      <c r="AG21" s="31"/>
     </row>
     <row r="22" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G22" s="32" t="s">
+      <c r="G22" s="30" t="s">
         <v>817</v>
       </c>
-      <c r="H22" s="32" t="s">
+      <c r="H22" s="30" t="s">
         <v>818</v>
       </c>
-      <c r="S22" s="32" t="s">
+      <c r="S22" s="30" t="s">
         <v>806</v>
       </c>
-      <c r="W22" s="34"/>
-      <c r="X22" s="34"/>
-      <c r="Y22" s="32"/>
-      <c r="AA22" s="40" t="s">
+      <c r="W22" s="31"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="30"/>
+      <c r="AA22" s="38" t="s">
         <v>897</v>
       </c>
-      <c r="AB22" s="40"/>
-      <c r="AC22" s="40"/>
-      <c r="AD22" s="40"/>
-      <c r="AF22" s="34"/>
-      <c r="AG22" s="34"/>
+      <c r="AB22" s="38"/>
+      <c r="AC22" s="38"/>
+      <c r="AD22" s="38"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="31"/>
     </row>
     <row r="23" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="30" t="s">
         <v>819</v>
       </c>
-      <c r="H23" s="32" t="s">
+      <c r="H23" s="30" t="s">
         <v>820</v>
       </c>
-      <c r="S23" s="32" t="s">
+      <c r="S23" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="W23" s="34"/>
-      <c r="X23" s="34"/>
-      <c r="Y23" s="32"/>
-      <c r="AA23" s="40" t="s">
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="30"/>
+      <c r="AA23" s="38" t="s">
         <v>898</v>
       </c>
-      <c r="AB23" s="40"/>
-      <c r="AC23" s="40"/>
-      <c r="AD23" s="40"/>
-      <c r="AF23" s="34"/>
-      <c r="AG23" s="34"/>
+      <c r="AB23" s="38"/>
+      <c r="AC23" s="38"/>
+      <c r="AD23" s="38"/>
+      <c r="AF23" s="31"/>
+      <c r="AG23" s="31"/>
     </row>
     <row r="24" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S24" s="32" t="s">
+      <c r="S24" s="30" t="s">
         <v>808</v>
       </c>
-      <c r="W24" s="34"/>
-      <c r="X24" s="34"/>
-      <c r="Y24" s="32"/>
-      <c r="AA24" s="40" t="s">
+      <c r="W24" s="31"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="30"/>
+      <c r="AA24" s="38" t="s">
         <v>899</v>
       </c>
-      <c r="AB24" s="40"/>
-      <c r="AC24" s="40"/>
-      <c r="AD24" s="40"/>
-      <c r="AF24" s="34"/>
-      <c r="AG24" s="34"/>
+      <c r="AB24" s="38"/>
+      <c r="AC24" s="38"/>
+      <c r="AD24" s="38"/>
+      <c r="AF24" s="31"/>
+      <c r="AG24" s="31"/>
     </row>
     <row r="25" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S25" s="32" t="s">
+      <c r="S25" s="30" t="s">
         <v>810</v>
       </c>
-      <c r="W25" s="34"/>
-      <c r="X25" s="34"/>
-      <c r="Y25" s="32"/>
-      <c r="AA25" s="40" t="s">
+      <c r="W25" s="31"/>
+      <c r="X25" s="31"/>
+      <c r="Y25" s="30"/>
+      <c r="AA25" s="38" t="s">
         <v>900</v>
       </c>
-      <c r="AB25" s="40"/>
-      <c r="AC25" s="40"/>
-      <c r="AD25" s="40"/>
-      <c r="AF25" s="34"/>
-      <c r="AG25" s="34"/>
+      <c r="AB25" s="38"/>
+      <c r="AC25" s="38"/>
+      <c r="AD25" s="38"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="31"/>
     </row>
     <row r="26" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S26" s="32" t="s">
+      <c r="S26" s="30" t="s">
         <v>396</v>
       </c>
-      <c r="W26" s="34"/>
-      <c r="X26" s="34"/>
-      <c r="Y26" s="32"/>
-      <c r="AA26" s="40" t="s">
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="30"/>
+      <c r="AA26" s="38" t="s">
         <v>901</v>
       </c>
-      <c r="AB26" s="40"/>
-      <c r="AC26" s="40"/>
-      <c r="AD26" s="40"/>
-      <c r="AF26" s="34"/>
-      <c r="AG26" s="34"/>
+      <c r="AB26" s="38"/>
+      <c r="AC26" s="38"/>
+      <c r="AD26" s="38"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="31"/>
     </row>
     <row r="27" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S27" s="32" t="s">
+      <c r="S27" s="30" t="s">
         <v>813</v>
       </c>
-      <c r="W27" s="34"/>
-      <c r="X27" s="34"/>
-      <c r="Y27" s="32"/>
-      <c r="AA27" s="40" t="s">
+      <c r="W27" s="31"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="30"/>
+      <c r="AA27" s="38" t="s">
         <v>902</v>
       </c>
-      <c r="AB27" s="40"/>
-      <c r="AC27" s="40"/>
-      <c r="AD27" s="40"/>
-      <c r="AF27" s="34"/>
-      <c r="AG27" s="34"/>
+      <c r="AB27" s="38"/>
+      <c r="AC27" s="38"/>
+      <c r="AD27" s="38"/>
+      <c r="AF27" s="31"/>
+      <c r="AG27" s="31"/>
     </row>
     <row r="28" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S28" s="32" t="s">
+      <c r="S28" s="30" t="s">
         <v>815</v>
       </c>
-      <c r="W28" s="34"/>
-      <c r="X28" s="34"/>
-      <c r="Y28" s="32"/>
-      <c r="AF28" s="34"/>
-      <c r="AG28" s="34"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="30"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
     </row>
     <row r="29" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S29" s="32" t="s">
+      <c r="S29" s="30" t="s">
         <v>817</v>
       </c>
-      <c r="W29" s="34"/>
-      <c r="X29" s="34"/>
-      <c r="Y29" s="32"/>
-      <c r="AA29" s="42" t="s">
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="30"/>
+      <c r="AA29" s="37" t="s">
         <v>903</v>
       </c>
-      <c r="AF29" s="34"/>
-      <c r="AG29" s="34"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="31"/>
     </row>
     <row r="30" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S30" s="32" t="s">
+      <c r="S30" s="30" t="s">
         <v>819</v>
       </c>
-      <c r="W30" s="34"/>
-      <c r="X30" s="34"/>
-      <c r="Y30" s="32"/>
-      <c r="AF30" s="34"/>
-      <c r="AG30" s="34"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="31"/>
+      <c r="Y30" s="30"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="31"/>
     </row>
     <row r="31" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="W31" s="34"/>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="32"/>
-      <c r="AF31" s="34"/>
-      <c r="AG31" s="34"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="30"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="31"/>
     </row>
     <row r="32" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="W32" s="34"/>
-      <c r="X32" s="34"/>
-      <c r="Y32" s="32"/>
-      <c r="AF32" s="34"/>
-      <c r="AG32" s="34"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="30"/>
+      <c r="AF32" s="31"/>
+      <c r="AG32" s="31"/>
     </row>
     <row r="33" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="W33" s="34"/>
-      <c r="X33" s="34"/>
-      <c r="Y33" s="32"/>
-      <c r="AF33" s="34"/>
-      <c r="AG33" s="34"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="30"/>
+      <c r="AF33" s="31"/>
+      <c r="AG33" s="31"/>
     </row>
     <row r="34" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF34" s="34"/>
-      <c r="AG34" s="34"/>
+      <c r="AF34" s="31"/>
+      <c r="AG34" s="31"/>
     </row>
     <row r="35" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF35" s="34"/>
-      <c r="AG35" s="34"/>
+      <c r="AF35" s="31"/>
+      <c r="AG35" s="31"/>
     </row>
     <row r="36" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF36" s="34"/>
-      <c r="AG36" s="34"/>
+      <c r="AF36" s="31"/>
+      <c r="AG36" s="31"/>
     </row>
     <row r="37" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF37" s="34"/>
-      <c r="AG37" s="34"/>
+      <c r="AF37" s="31"/>
+      <c r="AG37" s="31"/>
     </row>
     <row r="38" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF38" s="34"/>
-      <c r="AG38" s="34"/>
+      <c r="AF38" s="31"/>
+      <c r="AG38" s="31"/>
     </row>
     <row r="39" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF39" s="34"/>
-      <c r="AG39" s="34"/>
+      <c r="AF39" s="31"/>
+      <c r="AG39" s="31"/>
     </row>
     <row r="40" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF40" s="34"/>
-      <c r="AG40" s="34"/>
+      <c r="AF40" s="31"/>
+      <c r="AG40" s="31"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="12">
+    <mergeCell ref="AA21:AD21"/>
+    <mergeCell ref="AA22:AD22"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="AA16:AD16"/>
+    <mergeCell ref="AA17:AD17"/>
+    <mergeCell ref="AA18:AD18"/>
     <mergeCell ref="AA23:AD23"/>
     <mergeCell ref="AA24:AD24"/>
     <mergeCell ref="AA25:AD25"/>
     <mergeCell ref="AA26:AD26"/>
     <mergeCell ref="AA27:AD27"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="AA16:AD16"/>
-    <mergeCell ref="AA17:AD17"/>
-    <mergeCell ref="AA18:AD18"/>
-    <mergeCell ref="AA21:AD21"/>
-    <mergeCell ref="AA22:AD22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/reference/Unidades/plantilla_modelos_ZVEH_ZCAM.xlsx
+++ b/data/reference/Unidades/plantilla_modelos_ZVEH_ZCAM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tattersall-my.sharepoint.com/personal/sherrera_tattersall_cl/Documents/Escritorio/FACU/INPUTS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tattersall-my.sharepoint.com/personal/sherrera_tattersall_cl/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF803BB-BA08-4F01-AE46-9292D853ED64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{BDF803BB-BA08-4F01-AE46-9292D853ED64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81F2CB6E-27A3-4EF1-A4C4-050B0E24C7B7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2603" uniqueCount="934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2587" uniqueCount="918">
   <si>
     <t>FILIAL CODIGO</t>
   </si>
@@ -2125,18 +2125,6 @@
     <t>BASHAN</t>
   </si>
   <si>
-    <t>020</t>
-  </si>
-  <si>
-    <t>ASILE MASTER</t>
-  </si>
-  <si>
-    <t>030</t>
-  </si>
-  <si>
-    <t>COMBILIFT</t>
-  </si>
-  <si>
     <t>040</t>
   </si>
   <si>
@@ -2161,18 +2149,6 @@
     <t>080</t>
   </si>
   <si>
-    <t>090</t>
-  </si>
-  <si>
-    <t>HIDROMEK</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>HYSTER</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
@@ -2194,12 +2170,6 @@
     <t>LIFAN</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>LIUGONG</t>
-  </si>
-  <si>
     <t>160</t>
   </si>
   <si>
@@ -2212,12 +2182,6 @@
     <t>LYNK &amp; CO</t>
   </si>
   <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>MAXIMAL</t>
-  </si>
-  <si>
     <t>190</t>
   </si>
   <si>
@@ -2242,12 +2206,6 @@
     <t>RIDDARA</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>TERBERG</t>
-  </si>
-  <si>
     <t>240</t>
   </si>
   <si>
@@ -2311,9 +2269,6 @@
     <t>Unidad Nueva</t>
   </si>
   <si>
-    <t>Unidad Usada</t>
-  </si>
-  <si>
     <t>codigo</t>
   </si>
   <si>
@@ -2327,9 +2282,6 @@
   </si>
   <si>
     <t>52</t>
-  </si>
-  <si>
-    <t>53</t>
   </si>
   <si>
     <t>Tablas de conversión — se pueden ampliar agregando filas al final de cada tabla</t>
@@ -3572,31 +3524,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>919</v>
+        <v>903</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>920</v>
+        <v>904</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>740</v>
+        <v>726</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>741</v>
+        <v>727</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>739</v>
+        <v>725</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>743</v>
+        <v>729</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>904</v>
+        <v>888</v>
       </c>
       <c r="L1" s="18" t="s">
         <v>2</v>
@@ -3611,16 +3563,16 @@
         <v>5</v>
       </c>
       <c r="P1" s="18" t="s">
-        <v>738</v>
+        <v>724</v>
       </c>
       <c r="Q1" s="18" t="s">
-        <v>912</v>
+        <v>896</v>
       </c>
       <c r="R1" s="18" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="S1" s="18" t="s">
-        <v>913</v>
+        <v>897</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -3639,22 +3591,22 @@
         <v>XL3PLUS15KWH-1.2L-PHEV-6X2-DCT</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>910</v>
+        <v>894</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>911</v>
+        <v>895</v>
       </c>
       <c r="G2" s="19">
         <v>1200</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>906</v>
+        <v>890</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>789</v>
+        <v>773</v>
       </c>
       <c r="J2" s="19" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="K2" s="19">
         <v>15</v>
@@ -3666,13 +3618,13 @@
         <v>22</v>
       </c>
       <c r="N2" s="19" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="O2" s="19" t="s">
         <v>530</v>
       </c>
       <c r="P2" s="19" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="Q2" s="19">
         <v>1</v>
@@ -7287,12 +7239,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="11">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
-          <x14:formula1>
-            <xm:f>'Diccionario Marcas'!$B$2:$B$30</xm:f>
-          </x14:formula1>
-          <xm:sqref>N2:N1048576</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
             <xm:f>'Diccionario Fabricantes'!$C$2:$C$75</xm:f>
@@ -7310,12 +7256,6 @@
             <xm:f>'Diccionario Jerarquías'!$F$2:$F$350</xm:f>
           </x14:formula1>
           <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DDA9FFC1-DACA-4C4F-8833-E67B5AAA7A93}">
-          <x14:formula1>
-            <xm:f>'Diccionario GrupoImputacion'!$B$2:$B$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>P2:P1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C255865D-AF00-4300-85C8-E575D80773D0}">
           <x14:formula1>
@@ -7352,6 +7292,18 @@
             <xm:f>NPF!$U$4:$U$5</xm:f>
           </x14:formula1>
           <xm:sqref>Q2:Q500</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DDA9FFC1-DACA-4C4F-8833-E67B5AAA7A93}">
+          <x14:formula1>
+            <xm:f>'Diccionario GrupoImputacion'!$B$2:$B$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
+          <x14:formula1>
+            <xm:f>'Diccionario Marcas'!$B$2:$B$23</xm:f>
+          </x14:formula1>
+          <xm:sqref>N2:N1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7397,84 +7349,84 @@
   <sheetData>
     <row r="1" spans="1:33" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>755</v>
+        <v>739</v>
       </c>
       <c r="W1" s="25" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="AA1" s="26" t="s">
-        <v>858</v>
+        <v>842</v>
       </c>
       <c r="AF1" s="25" t="s">
-        <v>922</v>
+        <v>906</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="W2" s="39" t="s">
-        <v>822</v>
+        <v>806</v>
       </c>
       <c r="X2" s="39"/>
       <c r="Y2" s="39"/>
       <c r="AA2" s="27" t="s">
-        <v>859</v>
+        <v>843</v>
       </c>
       <c r="AF2" s="39" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
       <c r="AG2" s="39"/>
     </row>
     <row r="3" spans="1:33" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>756</v>
+        <v>740</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>757</v>
+        <v>741</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>758</v>
+        <v>742</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>757</v>
+        <v>741</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>759</v>
+        <v>743</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>757</v>
+        <v>741</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="N3" s="28" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="O3" s="29"/>
       <c r="Q3" s="28" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="U3" s="28" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="W3" s="28" t="s">
-        <v>823</v>
+        <v>807</v>
       </c>
       <c r="X3" s="28" t="s">
-        <v>824</v>
+        <v>808</v>
       </c>
       <c r="Y3" s="28" t="s">
-        <v>825</v>
+        <v>809</v>
       </c>
       <c r="AF3" s="28" t="s">
-        <v>924</v>
+        <v>908</v>
       </c>
       <c r="AG3" s="28" t="s">
-        <v>925</v>
+        <v>909</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -7482,22 +7434,22 @@
         <v>47</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="G4" s="30" t="s">
         <v>112</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>769</v>
+        <v>753</v>
       </c>
       <c r="J4" s="30" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="L4" s="30" t="s">
         <v>433</v>
@@ -7509,31 +7461,31 @@
         <v>432</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="S4" s="30" t="s">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="U4" s="30">
         <v>1</v>
       </c>
       <c r="W4" s="31" t="s">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="X4" s="31" t="s">
-        <v>827</v>
+        <v>811</v>
       </c>
       <c r="Y4" s="30" t="s">
-        <v>828</v>
+        <v>812</v>
       </c>
       <c r="AA4" s="32" t="s">
-        <v>860</v>
+        <v>844</v>
       </c>
       <c r="AF4" s="31" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="AG4" s="31" t="s">
-        <v>914</v>
+        <v>898</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -7541,22 +7493,22 @@
         <v>15</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>774</v>
+        <v>758</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="G5" s="30" t="s">
         <v>114</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="L5" s="30" t="s">
         <v>435</v>
@@ -7568,34 +7520,34 @@
         <v>434</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="S5" s="30" t="s">
-        <v>779</v>
+        <v>763</v>
       </c>
       <c r="U5" s="30">
         <v>2</v>
       </c>
       <c r="W5" s="31" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
       <c r="X5" s="31" t="s">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="Y5" s="30" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="AA5" s="28" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="AB5" s="28" t="s">
-        <v>861</v>
+        <v>845</v>
       </c>
       <c r="AC5" s="28" t="s">
-        <v>862</v>
+        <v>846</v>
       </c>
       <c r="AD5" s="28" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="AF5" s="31" t="s">
         <v>548</v>
@@ -7606,25 +7558,25 @@
     </row>
     <row r="6" spans="1:33" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>905</v>
+        <v>889</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>909</v>
+        <v>893</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="L6" s="30" t="s">
         <v>431</v>
@@ -7636,28 +7588,28 @@
         <v>436</v>
       </c>
       <c r="S6" s="30" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="W6" s="31" t="s">
-        <v>832</v>
+        <v>816</v>
       </c>
       <c r="X6" s="31" t="s">
-        <v>833</v>
+        <v>817</v>
       </c>
       <c r="Y6" s="30" t="s">
-        <v>834</v>
+        <v>818</v>
       </c>
       <c r="AA6" s="34" t="s">
-        <v>864</v>
+        <v>848</v>
       </c>
       <c r="AB6" s="34" t="s">
-        <v>865</v>
+        <v>849</v>
       </c>
       <c r="AC6" s="34" t="s">
-        <v>866</v>
+        <v>850</v>
       </c>
       <c r="AD6" s="35" t="s">
-        <v>917</v>
+        <v>901</v>
       </c>
       <c r="AF6" s="31" t="s">
         <v>521</v>
@@ -7668,25 +7620,25 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
-        <v>906</v>
+        <v>890</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="G7" s="30" t="s">
         <v>101</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>789</v>
+        <v>773</v>
       </c>
       <c r="L7" s="30" t="s">
         <v>437</v>
@@ -7698,132 +7650,132 @@
         <v>438</v>
       </c>
       <c r="S7" s="30" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
       <c r="W7" s="31" t="s">
-        <v>835</v>
+        <v>819</v>
       </c>
       <c r="X7" s="31" t="s">
-        <v>836</v>
+        <v>820</v>
       </c>
       <c r="Y7" s="30" t="s">
-        <v>837</v>
+        <v>821</v>
       </c>
       <c r="AA7" s="34" t="s">
-        <v>867</v>
+        <v>851</v>
       </c>
       <c r="AB7" s="34" t="s">
-        <v>868</v>
+        <v>852</v>
       </c>
       <c r="AC7" s="34" t="s">
-        <v>869</v>
+        <v>853</v>
       </c>
       <c r="AD7" s="34" t="s">
-        <v>870</v>
+        <v>854</v>
       </c>
       <c r="AF7" s="31" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="AG7" s="31" t="s">
-        <v>926</v>
+        <v>910</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
-        <v>907</v>
+        <v>891</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="N8" s="30"/>
       <c r="O8" s="36"/>
       <c r="S8" s="30" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="W8" s="31" t="s">
-        <v>838</v>
+        <v>822</v>
       </c>
       <c r="X8" s="31" t="s">
-        <v>839</v>
+        <v>823</v>
       </c>
       <c r="Y8" s="30" t="s">
-        <v>840</v>
+        <v>824</v>
       </c>
       <c r="AA8" s="35" t="s">
-        <v>915</v>
+        <v>899</v>
       </c>
       <c r="AB8" s="34" t="s">
-        <v>871</v>
+        <v>855</v>
       </c>
       <c r="AC8" s="35" t="s">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="AD8" s="34" t="s">
-        <v>872</v>
+        <v>856</v>
       </c>
       <c r="AF8" s="31" t="s">
-        <v>737</v>
+        <v>723</v>
       </c>
       <c r="AG8" s="31" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>908</v>
+        <v>892</v>
       </c>
       <c r="B9" s="30" t="s">
         <v>290</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="N9" s="30"/>
       <c r="O9" s="36"/>
       <c r="S9" s="30" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="W9" s="31" t="s">
-        <v>841</v>
+        <v>825</v>
       </c>
       <c r="X9" s="31" t="s">
-        <v>842</v>
+        <v>826</v>
       </c>
       <c r="Y9" s="30" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
       <c r="AA9" s="34" t="s">
-        <v>873</v>
+        <v>857</v>
       </c>
       <c r="AB9" s="34" t="s">
-        <v>874</v>
+        <v>858</v>
       </c>
       <c r="AC9" s="34" t="s">
-        <v>875</v>
+        <v>859</v>
       </c>
       <c r="AD9" s="34" t="s">
-        <v>876</v>
+        <v>860</v>
       </c>
       <c r="AF9" s="31" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="AG9" s="31" t="s">
-        <v>928</v>
+        <v>912</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -7837,42 +7789,42 @@
         <v>103</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>800</v>
+        <v>784</v>
       </c>
       <c r="J10" s="30" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="N10" s="30"/>
       <c r="O10" s="36"/>
       <c r="S10" s="30" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="W10" s="31" t="s">
-        <v>844</v>
+        <v>828</v>
       </c>
       <c r="X10" s="31" t="s">
-        <v>845</v>
+        <v>829</v>
       </c>
       <c r="Y10" s="30" t="s">
-        <v>846</v>
+        <v>830</v>
       </c>
       <c r="AA10" s="34" t="s">
-        <v>877</v>
+        <v>861</v>
       </c>
       <c r="AB10" s="34" t="s">
-        <v>878</v>
+        <v>862</v>
       </c>
       <c r="AC10" s="34" t="s">
-        <v>879</v>
+        <v>863</v>
       </c>
       <c r="AD10" s="34" t="s">
-        <v>880</v>
+        <v>864</v>
       </c>
       <c r="AF10" s="31" t="s">
         <v>685</v>
       </c>
       <c r="AG10" s="31" t="s">
-        <v>929</v>
+        <v>913</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -7880,37 +7832,37 @@
         <v>212</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="S11" s="30" t="s">
         <v>112</v>
       </c>
       <c r="W11" s="31" t="s">
-        <v>847</v>
+        <v>831</v>
       </c>
       <c r="X11" s="31" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="Y11" s="30" t="s">
-        <v>846</v>
+        <v>830</v>
       </c>
       <c r="AA11" s="34" t="s">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="AB11" s="34" t="s">
-        <v>882</v>
+        <v>866</v>
       </c>
       <c r="AC11" s="34" t="s">
-        <v>883</v>
+        <v>867</v>
       </c>
       <c r="AD11" s="34" t="s">
-        <v>884</v>
+        <v>868</v>
       </c>
       <c r="AF11" s="31" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="AG11" s="31" t="s">
-        <v>930</v>
+        <v>914</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -7918,37 +7870,37 @@
         <v>118</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>803</v>
+        <v>787</v>
       </c>
       <c r="S12" s="30" t="s">
         <v>114</v>
       </c>
       <c r="W12" s="31" t="s">
-        <v>849</v>
+        <v>833</v>
       </c>
       <c r="X12" s="31" t="s">
-        <v>850</v>
+        <v>834</v>
       </c>
       <c r="Y12" s="30" t="s">
-        <v>851</v>
+        <v>835</v>
       </c>
       <c r="AA12" s="34" t="s">
-        <v>885</v>
+        <v>869</v>
       </c>
       <c r="AB12" s="34" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="AC12" s="34" t="s">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="AD12" s="34" t="s">
-        <v>887</v>
+        <v>871</v>
       </c>
       <c r="AF12" s="31" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="AG12" s="31" t="s">
-        <v>931</v>
+        <v>915</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -7956,34 +7908,34 @@
         <v>304</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="S13" s="30" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="W13" s="31" t="s">
-        <v>852</v>
+        <v>836</v>
       </c>
       <c r="X13" s="31" t="s">
-        <v>853</v>
+        <v>837</v>
       </c>
       <c r="Y13" s="30" t="s">
-        <v>854</v>
+        <v>838</v>
       </c>
       <c r="AA13" s="34" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
       <c r="AB13" s="34" t="s">
-        <v>889</v>
+        <v>873</v>
       </c>
       <c r="AC13" s="34" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
       <c r="AD13" s="34" t="s">
-        <v>891</v>
+        <v>875</v>
       </c>
       <c r="AF13" s="31" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="AG13" s="31" t="s">
         <v>545</v>
@@ -7994,48 +7946,48 @@
         <v>214</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="S14" s="30" t="s">
         <v>101</v>
       </c>
       <c r="W14" s="31" t="s">
-        <v>855</v>
+        <v>839</v>
       </c>
       <c r="X14" s="31" t="s">
-        <v>856</v>
+        <v>840</v>
       </c>
       <c r="Y14" s="30" t="s">
-        <v>857</v>
+        <v>841</v>
       </c>
       <c r="AF14" s="31" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="AG14" s="31" t="s">
-        <v>932</v>
+        <v>916</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="G15" s="30" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="H15" s="30" t="s">
         <v>107</v>
       </c>
       <c r="S15" s="30" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="W15" s="31"/>
       <c r="X15" s="31"/>
       <c r="Y15" s="30"/>
       <c r="AA15" s="32" t="s">
-        <v>892</v>
+        <v>876</v>
       </c>
       <c r="AF15" s="31" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="AG15" s="31" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -8043,16 +7995,16 @@
         <v>120</v>
       </c>
       <c r="H16" s="30" t="s">
-        <v>807</v>
+        <v>791</v>
       </c>
       <c r="S16" s="30" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="W16" s="31"/>
       <c r="X16" s="31"/>
       <c r="Y16" s="30"/>
       <c r="AA16" s="38" t="s">
-        <v>893</v>
+        <v>877</v>
       </c>
       <c r="AB16" s="38"/>
       <c r="AC16" s="38"/>
@@ -8061,15 +8013,15 @@
         <v>680</v>
       </c>
       <c r="AG16" s="31" t="s">
-        <v>933</v>
+        <v>917</v>
       </c>
     </row>
     <row r="17" spans="7:33" x14ac:dyDescent="0.25">
       <c r="G17" s="30" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="H17" s="30" t="s">
-        <v>809</v>
+        <v>793</v>
       </c>
       <c r="S17" s="30" t="s">
         <v>103</v>
@@ -8078,7 +8030,7 @@
       <c r="X17" s="31"/>
       <c r="Y17" s="30"/>
       <c r="AA17" s="38" t="s">
-        <v>894</v>
+        <v>878</v>
       </c>
       <c r="AB17" s="38"/>
       <c r="AC17" s="38"/>
@@ -8088,10 +8040,10 @@
     </row>
     <row r="18" spans="7:33" x14ac:dyDescent="0.25">
       <c r="G18" s="30" t="s">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>811</v>
+        <v>795</v>
       </c>
       <c r="S18" s="30" t="s">
         <v>212</v>
@@ -8100,7 +8052,7 @@
       <c r="X18" s="31"/>
       <c r="Y18" s="30"/>
       <c r="AA18" s="40" t="s">
-        <v>918</v>
+        <v>902</v>
       </c>
       <c r="AB18" s="38"/>
       <c r="AC18" s="38"/>
@@ -8113,7 +8065,7 @@
         <v>396</v>
       </c>
       <c r="H19" s="30" t="s">
-        <v>812</v>
+        <v>796</v>
       </c>
       <c r="S19" s="30" t="s">
         <v>118</v>
@@ -8126,10 +8078,10 @@
     </row>
     <row r="20" spans="7:33" x14ac:dyDescent="0.25">
       <c r="G20" s="30" t="s">
-        <v>813</v>
+        <v>797</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>814</v>
+        <v>798</v>
       </c>
       <c r="S20" s="30" t="s">
         <v>304</v>
@@ -8138,17 +8090,17 @@
       <c r="X20" s="31"/>
       <c r="Y20" s="30"/>
       <c r="AA20" s="32" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
       <c r="AF20" s="31"/>
       <c r="AG20" s="31"/>
     </row>
     <row r="21" spans="7:33" x14ac:dyDescent="0.25">
       <c r="G21" s="30" t="s">
-        <v>815</v>
+        <v>799</v>
       </c>
       <c r="H21" s="30" t="s">
-        <v>816</v>
+        <v>800</v>
       </c>
       <c r="S21" s="30" t="s">
         <v>214</v>
@@ -8157,7 +8109,7 @@
       <c r="X21" s="31"/>
       <c r="Y21" s="30"/>
       <c r="AA21" s="38" t="s">
-        <v>896</v>
+        <v>880</v>
       </c>
       <c r="AB21" s="38"/>
       <c r="AC21" s="38"/>
@@ -8167,19 +8119,19 @@
     </row>
     <row r="22" spans="7:33" x14ac:dyDescent="0.25">
       <c r="G22" s="30" t="s">
-        <v>817</v>
+        <v>801</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>818</v>
+        <v>802</v>
       </c>
       <c r="S22" s="30" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="W22" s="31"/>
       <c r="X22" s="31"/>
       <c r="Y22" s="30"/>
       <c r="AA22" s="38" t="s">
-        <v>897</v>
+        <v>881</v>
       </c>
       <c r="AB22" s="38"/>
       <c r="AC22" s="38"/>
@@ -8189,10 +8141,10 @@
     </row>
     <row r="23" spans="7:33" x14ac:dyDescent="0.25">
       <c r="G23" s="30" t="s">
-        <v>819</v>
+        <v>803</v>
       </c>
       <c r="H23" s="30" t="s">
-        <v>820</v>
+        <v>804</v>
       </c>
       <c r="S23" s="30" t="s">
         <v>120</v>
@@ -8201,7 +8153,7 @@
       <c r="X23" s="31"/>
       <c r="Y23" s="30"/>
       <c r="AA23" s="38" t="s">
-        <v>898</v>
+        <v>882</v>
       </c>
       <c r="AB23" s="38"/>
       <c r="AC23" s="38"/>
@@ -8211,13 +8163,13 @@
     </row>
     <row r="24" spans="7:33" x14ac:dyDescent="0.25">
       <c r="S24" s="30" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="W24" s="31"/>
       <c r="X24" s="31"/>
       <c r="Y24" s="30"/>
       <c r="AA24" s="38" t="s">
-        <v>899</v>
+        <v>883</v>
       </c>
       <c r="AB24" s="38"/>
       <c r="AC24" s="38"/>
@@ -8227,13 +8179,13 @@
     </row>
     <row r="25" spans="7:33" x14ac:dyDescent="0.25">
       <c r="S25" s="30" t="s">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="W25" s="31"/>
       <c r="X25" s="31"/>
       <c r="Y25" s="30"/>
       <c r="AA25" s="38" t="s">
-        <v>900</v>
+        <v>884</v>
       </c>
       <c r="AB25" s="38"/>
       <c r="AC25" s="38"/>
@@ -8249,7 +8201,7 @@
       <c r="X26" s="31"/>
       <c r="Y26" s="30"/>
       <c r="AA26" s="38" t="s">
-        <v>901</v>
+        <v>885</v>
       </c>
       <c r="AB26" s="38"/>
       <c r="AC26" s="38"/>
@@ -8259,13 +8211,13 @@
     </row>
     <row r="27" spans="7:33" x14ac:dyDescent="0.25">
       <c r="S27" s="30" t="s">
-        <v>813</v>
+        <v>797</v>
       </c>
       <c r="W27" s="31"/>
       <c r="X27" s="31"/>
       <c r="Y27" s="30"/>
       <c r="AA27" s="38" t="s">
-        <v>902</v>
+        <v>886</v>
       </c>
       <c r="AB27" s="38"/>
       <c r="AC27" s="38"/>
@@ -8275,7 +8227,7 @@
     </row>
     <row r="28" spans="7:33" x14ac:dyDescent="0.25">
       <c r="S28" s="30" t="s">
-        <v>815</v>
+        <v>799</v>
       </c>
       <c r="W28" s="31"/>
       <c r="X28" s="31"/>
@@ -8285,20 +8237,20 @@
     </row>
     <row r="29" spans="7:33" x14ac:dyDescent="0.25">
       <c r="S29" s="30" t="s">
-        <v>817</v>
+        <v>801</v>
       </c>
       <c r="W29" s="31"/>
       <c r="X29" s="31"/>
       <c r="Y29" s="30"/>
       <c r="AA29" s="37" t="s">
-        <v>903</v>
+        <v>887</v>
       </c>
       <c r="AF29" s="31"/>
       <c r="AG29" s="31"/>
     </row>
     <row r="30" spans="7:33" x14ac:dyDescent="0.25">
       <c r="S30" s="30" t="s">
-        <v>819</v>
+        <v>803</v>
       </c>
       <c r="W30" s="31"/>
       <c r="X30" s="31"/>
@@ -8358,6 +8310,11 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="12">
+    <mergeCell ref="AA23:AD23"/>
+    <mergeCell ref="AA24:AD24"/>
+    <mergeCell ref="AA25:AD25"/>
+    <mergeCell ref="AA26:AD26"/>
+    <mergeCell ref="AA27:AD27"/>
     <mergeCell ref="AA21:AD21"/>
     <mergeCell ref="AA22:AD22"/>
     <mergeCell ref="AF2:AG2"/>
@@ -8365,11 +8322,6 @@
     <mergeCell ref="AA16:AD16"/>
     <mergeCell ref="AA17:AD17"/>
     <mergeCell ref="AA18:AD18"/>
-    <mergeCell ref="AA23:AD23"/>
-    <mergeCell ref="AA24:AD24"/>
-    <mergeCell ref="AA25:AD25"/>
-    <mergeCell ref="AA26:AD26"/>
-    <mergeCell ref="AA27:AD27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -16261,7 +16213,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -16289,23 +16241,23 @@
         <v>686</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>687</v>
+        <v>564</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
+        <v>687</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>688</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
+        <v>689</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>690</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -16320,24 +16272,24 @@
       <c r="A7" s="11" t="s">
         <v>693</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>694</v>
+      <c r="B7" s="6" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
+        <v>694</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>695</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
+        <v>696</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>697</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -16345,39 +16297,39 @@
         <v>698</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>699</v>
+        <v>521</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>700</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>702</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>704</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
+        <v>705</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>706</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -16441,72 +16393,44 @@
         <v>721</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="B23" s="14" t="s">
         <v>723</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>724</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
-        <v>725</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>726</v>
-      </c>
+      <c r="A24" s="15"/>
+      <c r="B24" s="2"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>727</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>728</v>
-      </c>
+      <c r="A25" s="15"/>
+      <c r="B25" s="7"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>729</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>730</v>
-      </c>
+      <c r="A26" s="15"/>
+      <c r="B26" s="7"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>731</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>732</v>
-      </c>
+      <c r="A27" s="15"/>
+      <c r="B27" s="7"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>733</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>734</v>
-      </c>
+      <c r="A28" s="15"/>
+      <c r="B28" s="7"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
-        <v>735</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>680</v>
-      </c>
+      <c r="A29" s="15"/>
+      <c r="B29" s="7"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>736</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>737</v>
-      </c>
+      <c r="A30" s="15"/>
+      <c r="B30" s="2"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="15"/>
@@ -16514,23 +16438,23 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="15"/>
-      <c r="B32" s="7"/>
+      <c r="B32" s="2"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="15"/>
-      <c r="B33" s="7"/>
+      <c r="B33" s="2"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="15"/>
-      <c r="B34" s="7"/>
+      <c r="B34" s="2"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="15"/>
-      <c r="B35" s="7"/>
+      <c r="B35" s="2"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
-      <c r="B36" s="7"/>
+      <c r="B36" s="2"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="15"/>
@@ -16661,32 +16585,32 @@
       <c r="B68" s="2"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
-      <c r="B69" s="2"/>
+      <c r="A69" s="16"/>
+      <c r="B69" s="4"/>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="15"/>
-      <c r="B70" s="2"/>
+      <c r="A70" s="16"/>
+      <c r="B70" s="4"/>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
-      <c r="B71" s="2"/>
+      <c r="A71" s="16"/>
+      <c r="B71" s="4"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="15"/>
-      <c r="B72" s="2"/>
+      <c r="A72" s="16"/>
+      <c r="B72" s="4"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
-      <c r="B73" s="2"/>
+      <c r="A73" s="16"/>
+      <c r="B73" s="4"/>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="15"/>
-      <c r="B74" s="2"/>
+      <c r="A74" s="16"/>
+      <c r="B74" s="4"/>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
-      <c r="B75" s="2"/>
+      <c r="A75" s="16"/>
+      <c r="B75" s="4"/>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="16"/>
@@ -16715,34 +16639,6 @@
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="16"/>
       <c r="B82" s="4"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="16"/>
-      <c r="B83" s="4"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="16"/>
-      <c r="B84" s="4"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="16"/>
-      <c r="B85" s="4"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="16"/>
-      <c r="B86" s="4"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="16"/>
-      <c r="B87" s="4"/>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="16"/>
-      <c r="B88" s="4"/>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="16"/>
-      <c r="B89" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16751,7 +16647,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418957F0-6579-4672-9A5D-D437B1383D8B}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="17"/>
@@ -16759,42 +16655,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>749</v>
+        <v>734</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>754</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/data/reference/Unidades/plantilla_modelos_ZVEH_ZCAM.xlsx
+++ b/data/reference/Unidades/plantilla_modelos_ZVEH_ZCAM.xlsx
@@ -13396,7 +13396,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -13446,17 +13446,6 @@
       </c>
       <c r="C4" s="6" t="s">
         <v>551</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>552</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>554</v>
       </c>
     </row>
   </sheetData>
